--- a/runtime.dat/Reaction/Reactions.xlsx
+++ b/runtime.dat/Reaction/Reactions.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Euler-SYCL\runtime.dat\Reaction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\XFLUIDS\runtime.dat\Reaction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEECDB3-4D6B-47B6-A486-301283F502D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1641575A-BE5B-4103-9AD1-0D6CD0F755E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="H2O_18_Reaction" sheetId="4" r:id="rId1"/>
     <sheet name="H2O_19_Reaction" sheetId="1" r:id="rId2"/>
     <sheet name="H2O_21_Reaction" sheetId="2" r:id="rId3"/>
     <sheet name="H2O_23_Reaction" sheetId="3" r:id="rId4"/>
+    <sheet name="H2O-N2_19_Reaction" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="42">
   <si>
     <t xml:space="preserve">H2    </t>
   </si>
@@ -159,7 +160,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,6 +317,23 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -745,7 +763,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -767,6 +785,27 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -787,30 +826,30 @@
     <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
     <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
     <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
     <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
     <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1123,7 +1162,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5977D6-625A-4B51-AC0B-2BFDB941363F}">
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="2" bestFit="1" customWidth="1"/>
@@ -1131,7 +1170,7 @@
     <col min="4" max="9" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -1163,7 +1202,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.2" customHeight="1">
+    <row r="2" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -1195,7 +1234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="13.2" customHeight="1">
+    <row r="3" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>6</v>
       </c>
@@ -1227,7 +1266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1256,7 +1295,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1285,12 +1324,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -1322,7 +1361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -1354,7 +1393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>0</v>
       </c>
@@ -1386,7 +1425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>1</v>
       </c>
@@ -1418,7 +1457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>0</v>
       </c>
@@ -1450,7 +1489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0</v>
       </c>
@@ -1482,7 +1521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>0</v>
       </c>
@@ -1514,7 +1553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>0</v>
       </c>
@@ -1546,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>0</v>
       </c>
@@ -1578,7 +1617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>0</v>
       </c>
@@ -1610,7 +1649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1</v>
       </c>
@@ -1642,7 +1681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>0</v>
       </c>
@@ -1674,7 +1713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>0</v>
       </c>
@@ -1706,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>0</v>
       </c>
@@ -1738,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>0</v>
       </c>
@@ -1770,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>0</v>
       </c>
@@ -1802,7 +1841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>0</v>
       </c>
@@ -1834,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>0</v>
       </c>
@@ -1866,12 +1905,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>0</v>
       </c>
@@ -1903,7 +1942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>0</v>
       </c>
@@ -1935,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>0</v>
       </c>
@@ -1967,7 +2006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>0</v>
       </c>
@@ -1999,7 +2038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>0</v>
       </c>
@@ -2031,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>0</v>
       </c>
@@ -2063,7 +2102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>0</v>
       </c>
@@ -2095,7 +2134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>0</v>
       </c>
@@ -2127,7 +2166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>0</v>
       </c>
@@ -2159,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>0</v>
       </c>
@@ -2191,7 +2230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>0</v>
       </c>
@@ -2223,7 +2262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>0</v>
       </c>
@@ -2255,7 +2294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>0</v>
       </c>
@@ -2287,7 +2326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>1</v>
       </c>
@@ -2319,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>0</v>
       </c>
@@ -2351,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>0</v>
       </c>
@@ -2383,7 +2422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>1</v>
       </c>
@@ -2415,7 +2454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>0</v>
       </c>
@@ -2447,12 +2486,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>0</v>
       </c>
@@ -2484,7 +2523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>0</v>
       </c>
@@ -2516,7 +2555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>0</v>
       </c>
@@ -2548,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>0</v>
       </c>
@@ -2580,7 +2619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>3.3</v>
       </c>
@@ -2612,7 +2651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>0</v>
       </c>
@@ -2644,7 +2683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>0</v>
       </c>
@@ -2676,7 +2715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>0</v>
       </c>
@@ -2708,7 +2747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>0</v>
       </c>
@@ -2740,7 +2779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>0</v>
       </c>
@@ -2772,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>3</v>
       </c>
@@ -2804,7 +2843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>1</v>
       </c>
@@ -2836,7 +2875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>1</v>
       </c>
@@ -2868,7 +2907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>0</v>
       </c>
@@ -2900,7 +2939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>0</v>
       </c>
@@ -2932,7 +2971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>1</v>
       </c>
@@ -2964,7 +3003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>0</v>
       </c>
@@ -2996,7 +3035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>0</v>
       </c>
@@ -3028,12 +3067,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>17000000000000</v>
       </c>
@@ -3044,7 +3083,7 @@
         <v>47780</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>1170000000</v>
       </c>
@@ -3055,7 +3094,7 @@
         <v>3626</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>5.13E+16</v>
       </c>
@@ -3066,7 +3105,7 @@
         <v>16507</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>18000000000</v>
       </c>
@@ -3077,7 +3116,7 @@
         <v>8826</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>2.1E+18</v>
       </c>
@@ -3088,7 +3127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>6.7E+19</v>
       </c>
@@ -3099,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>50000000000000</v>
       </c>
@@ -3110,7 +3149,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>250000000000000</v>
       </c>
@@ -3121,7 +3160,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>48000000000000</v>
       </c>
@@ -3132,7 +3171,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>600000000</v>
       </c>
@@ -3143,7 +3182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>2230000000000</v>
       </c>
@@ -3154,7 +3193,7 @@
         <v>92600</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>185000000000</v>
       </c>
@@ -3165,7 +3204,7 @@
         <v>95560</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>7.4999999999999999E+23</v>
       </c>
@@ -3176,7 +3215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>25000000000000</v>
       </c>
@@ -3187,7 +3226,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>2000000000000</v>
       </c>
@@ -3198,7 +3237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>1.3E+17</v>
       </c>
@@ -3209,7 +3248,7 @@
         <v>45500</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>1600000000000</v>
       </c>
@@ -3220,7 +3259,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>10000000000000</v>
       </c>
@@ -3240,13 +3279,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J98"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3278,7 +3317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -3307,12 +3346,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -3344,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3376,7 +3415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3408,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0</v>
       </c>
@@ -3440,7 +3479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3472,7 +3511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0</v>
       </c>
@@ -3504,7 +3543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0</v>
       </c>
@@ -3536,7 +3575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0</v>
       </c>
@@ -3568,7 +3607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0</v>
       </c>
@@ -3600,7 +3639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0</v>
       </c>
@@ -3632,7 +3671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0</v>
       </c>
@@ -3664,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0</v>
       </c>
@@ -3696,7 +3735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0</v>
       </c>
@@ -3728,7 +3767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
@@ -3760,7 +3799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0</v>
       </c>
@@ -3792,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0</v>
       </c>
@@ -3824,7 +3863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>0</v>
       </c>
@@ -3856,7 +3895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0</v>
       </c>
@@ -3888,7 +3927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>0</v>
       </c>
@@ -3920,7 +3959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>0</v>
       </c>
@@ -3952,7 +3991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>0</v>
       </c>
@@ -3984,7 +4023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>0</v>
       </c>
@@ -4016,7 +4055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>0</v>
       </c>
@@ -4048,12 +4087,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>0</v>
       </c>
@@ -4085,7 +4124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>0</v>
       </c>
@@ -4117,7 +4156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>0</v>
       </c>
@@ -4149,7 +4188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>0</v>
       </c>
@@ -4181,7 +4220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>0</v>
       </c>
@@ -4213,7 +4252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>0</v>
       </c>
@@ -4245,7 +4284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>0</v>
       </c>
@@ -4277,7 +4316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>0</v>
       </c>
@@ -4309,7 +4348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>0</v>
       </c>
@@ -4341,7 +4380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0</v>
       </c>
@@ -4373,7 +4412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1</v>
       </c>
@@ -4405,7 +4444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>0</v>
       </c>
@@ -4437,7 +4476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0</v>
       </c>
@@ -4469,7 +4508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>0</v>
       </c>
@@ -4501,7 +4540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0</v>
       </c>
@@ -4533,7 +4572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>0</v>
       </c>
@@ -4565,7 +4604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>0</v>
       </c>
@@ -4597,7 +4636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>0</v>
       </c>
@@ -4629,7 +4668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>0</v>
       </c>
@@ -4661,7 +4700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1</v>
       </c>
@@ -4693,7 +4732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>0</v>
       </c>
@@ -4725,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>0</v>
       </c>
@@ -4757,7 +4796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>0</v>
       </c>
@@ -4789,12 +4828,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>0</v>
       </c>
@@ -4826,7 +4865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>0</v>
       </c>
@@ -4858,7 +4897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>0</v>
       </c>
@@ -4890,7 +4929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>0</v>
       </c>
@@ -4922,7 +4961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2.5</v>
       </c>
@@ -4954,7 +4993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2.5</v>
       </c>
@@ -4986,7 +5025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2.5</v>
       </c>
@@ -5018,7 +5057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>0.73</v>
       </c>
@@ -5050,7 +5089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>1.3</v>
       </c>
@@ -5082,7 +5121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1.3</v>
       </c>
@@ -5114,7 +5153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>0</v>
       </c>
@@ -5146,7 +5185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>0</v>
       </c>
@@ -5178,7 +5217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>0</v>
       </c>
@@ -5210,7 +5249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>0</v>
       </c>
@@ -5242,7 +5281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>0</v>
       </c>
@@ -5274,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>0</v>
       </c>
@@ -5306,7 +5345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2.5</v>
       </c>
@@ -5338,7 +5377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2.5</v>
       </c>
@@ -5370,7 +5409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>0</v>
       </c>
@@ -5402,7 +5441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>0</v>
       </c>
@@ -5434,7 +5473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>0</v>
       </c>
@@ -5466,7 +5505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>0</v>
       </c>
@@ -5498,7 +5537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>0</v>
       </c>
@@ -5530,12 +5569,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>191000000000000</v>
       </c>
@@ -5546,7 +5585,7 @@
         <v>16440</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>50800</v>
       </c>
@@ -5560,7 +5599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>216000000</v>
       </c>
@@ -5574,7 +5613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>2970000</v>
       </c>
@@ -5585,7 +5624,7 @@
         <v>13400</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>4.57E+19</v>
       </c>
@@ -5596,7 +5635,7 @@
         <v>105100</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>6170000000000000</v>
       </c>
@@ -5607,7 +5646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>4.72E+18</v>
       </c>
@@ -5618,7 +5657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>4.4999999999999998E+22</v>
       </c>
@@ -5629,7 +5668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>3.48E+16</v>
       </c>
@@ -5640,7 +5679,7 @@
         <v>-1120</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>1480000000000</v>
       </c>
@@ -5654,7 +5693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>16600000000000</v>
       </c>
@@ -5668,7 +5707,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>70800000000000</v>
       </c>
@@ -5682,7 +5721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>32500000000000</v>
       </c>
@@ -5696,7 +5735,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>28900000000000</v>
       </c>
@@ -5710,7 +5749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>420000000000000</v>
       </c>
@@ -5721,7 +5760,7 @@
         <v>11980</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>130000000000</v>
       </c>
@@ -5732,7 +5771,7 @@
         <v>-1629</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>1.27E+17</v>
       </c>
@@ -5743,7 +5782,7 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>295000000000000</v>
       </c>
@@ -5754,7 +5793,7 @@
         <v>48400</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>24100000000000</v>
       </c>
@@ -5768,7 +5807,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>60300000000000</v>
       </c>
@@ -5782,7 +5821,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>9550000</v>
       </c>
@@ -5793,7 +5832,7 @@
         <v>3970</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>1000000000000</v>
       </c>
@@ -5807,7 +5846,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>580000000000000</v>
       </c>
@@ -5830,7 +5869,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I113"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="2"/>
     <col min="2" max="2" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -5838,7 +5877,7 @@
     <col min="4" max="9" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -5867,7 +5906,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -5896,12 +5935,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>0</v>
       </c>
@@ -5930,7 +5969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -5959,7 +5998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -5988,7 +6027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>0</v>
       </c>
@@ -6017,7 +6056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -6046,7 +6085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>0</v>
       </c>
@@ -6075,7 +6114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>0</v>
       </c>
@@ -6104,7 +6143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>0</v>
       </c>
@@ -6133,7 +6172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0</v>
       </c>
@@ -6162,7 +6201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>0</v>
       </c>
@@ -6191,7 +6230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>0</v>
       </c>
@@ -6220,7 +6259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>0</v>
       </c>
@@ -6249,7 +6288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>0</v>
       </c>
@@ -6278,7 +6317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>0</v>
       </c>
@@ -6307,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>0</v>
       </c>
@@ -6336,7 +6375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>0</v>
       </c>
@@ -6365,7 +6404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>0</v>
       </c>
@@ -6394,7 +6433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>0</v>
       </c>
@@ -6423,7 +6462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>0</v>
       </c>
@@ -6452,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>0</v>
       </c>
@@ -6481,7 +6520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>0</v>
       </c>
@@ -6510,12 +6549,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>0</v>
       </c>
@@ -6544,7 +6583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>0</v>
       </c>
@@ -6573,7 +6612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>0</v>
       </c>
@@ -6602,7 +6641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>0</v>
       </c>
@@ -6631,7 +6670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>0</v>
       </c>
@@ -6660,7 +6699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>0</v>
       </c>
@@ -6689,7 +6728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>0</v>
       </c>
@@ -6718,7 +6757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>0</v>
       </c>
@@ -6747,7 +6786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>0</v>
       </c>
@@ -6776,7 +6815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>1</v>
       </c>
@@ -6805,7 +6844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>0</v>
       </c>
@@ -6834,7 +6873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>0</v>
       </c>
@@ -6863,7 +6902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>0</v>
       </c>
@@ -6892,7 +6931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>0</v>
       </c>
@@ -6921,7 +6960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>0</v>
       </c>
@@ -6950,7 +6989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>0</v>
       </c>
@@ -6979,7 +7018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>0</v>
       </c>
@@ -7008,7 +7047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>1</v>
       </c>
@@ -7037,7 +7076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>0</v>
       </c>
@@ -7066,7 +7105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>0</v>
       </c>
@@ -7095,7 +7134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>0</v>
       </c>
@@ -7124,12 +7163,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>0</v>
       </c>
@@ -7158,7 +7197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>0</v>
       </c>
@@ -7187,7 +7226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>0</v>
       </c>
@@ -7216,7 +7255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>0</v>
       </c>
@@ -7245,7 +7284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>2.5</v>
       </c>
@@ -7274,7 +7313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>2.5</v>
       </c>
@@ -7303,7 +7342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>2.5</v>
       </c>
@@ -7332,7 +7371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>0.73</v>
       </c>
@@ -7361,7 +7400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>1.3</v>
       </c>
@@ -7390,7 +7429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>0</v>
       </c>
@@ -7419,7 +7458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>0</v>
       </c>
@@ -7448,7 +7487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>0</v>
       </c>
@@ -7477,7 +7516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>0</v>
       </c>
@@ -7506,7 +7545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>0</v>
       </c>
@@ -7535,7 +7574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>0</v>
       </c>
@@ -7564,7 +7603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>2.5</v>
       </c>
@@ -7593,7 +7632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>0</v>
       </c>
@@ -7622,7 +7661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>0</v>
       </c>
@@ -7651,7 +7690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>0</v>
       </c>
@@ -7680,7 +7719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>0</v>
       </c>
@@ -7709,7 +7748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>0</v>
       </c>
@@ -7738,12 +7777,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>191000000000000</v>
       </c>
@@ -7754,7 +7793,7 @@
         <v>16440</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>50800</v>
       </c>
@@ -7768,7 +7807,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>216000000</v>
       </c>
@@ -7782,7 +7821,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>2970000</v>
       </c>
@@ -7793,7 +7832,7 @@
         <v>13400</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>30</v>
       </c>
@@ -7802,7 +7841,7 @@
       </c>
       <c r="C74" s="4"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>31</v>
       </c>
@@ -7811,7 +7850,7 @@
       </c>
       <c r="C75" s="4"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>32</v>
       </c>
@@ -7820,7 +7859,7 @@
       </c>
       <c r="C76" s="4"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>33</v>
       </c>
@@ -7829,7 +7868,7 @@
       </c>
       <c r="C77" s="4"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>1480000000000</v>
       </c>
@@ -7843,7 +7882,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>16600000000000</v>
       </c>
@@ -7857,7 +7896,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>70800000000000</v>
       </c>
@@ -7868,7 +7907,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>32500000000000</v>
       </c>
@@ -7882,7 +7921,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>28900000000000</v>
       </c>
@@ -7896,7 +7935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>34</v>
       </c>
@@ -7905,7 +7944,7 @@
       </c>
       <c r="C83" s="4"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>35</v>
       </c>
@@ -7914,7 +7953,7 @@
       </c>
       <c r="C84" s="4"/>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>295000000000000</v>
       </c>
@@ -7925,7 +7964,7 @@
         <v>48430</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>24100000000000</v>
       </c>
@@ -7939,7 +7978,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>60300000000000</v>
       </c>
@@ -7953,7 +7992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>9550000</v>
       </c>
@@ -7964,7 +8003,7 @@
         <v>3970</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>1000000000000</v>
       </c>
@@ -7978,7 +8017,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>10700000000000</v>
       </c>
@@ -7992,12 +8031,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>0</v>
       </c>
@@ -8026,7 +8065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>0</v>
       </c>
@@ -8055,7 +8094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>0</v>
       </c>
@@ -8084,7 +8123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>0</v>
       </c>
@@ -8113,7 +8152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>2.5</v>
       </c>
@@ -8142,7 +8181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>2.5</v>
       </c>
@@ -8171,7 +8210,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>2.5</v>
       </c>
@@ -8200,7 +8239,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>0.73</v>
       </c>
@@ -8229,7 +8268,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>1.3</v>
       </c>
@@ -8258,7 +8297,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>0</v>
       </c>
@@ -8287,7 +8326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>0</v>
       </c>
@@ -8316,7 +8355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>0</v>
       </c>
@@ -8345,7 +8384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>0</v>
       </c>
@@ -8374,7 +8413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>0</v>
       </c>
@@ -8403,7 +8442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>0</v>
       </c>
@@ -8432,7 +8471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>2.5</v>
       </c>
@@ -8461,7 +8500,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>0</v>
       </c>
@@ -8490,7 +8529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>0</v>
       </c>
@@ -8519,7 +8558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>0</v>
       </c>
@@ -8548,7 +8587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>0</v>
       </c>
@@ -8577,7 +8616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>0</v>
       </c>
@@ -8615,7 +8654,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I98"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -8623,7 +8662,7 @@
     <col min="4" max="9" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8652,7 +8691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -8681,12 +8720,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>0</v>
       </c>
@@ -8715,7 +8754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -8744,7 +8783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -8773,7 +8812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>0</v>
       </c>
@@ -8802,7 +8841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -8831,7 +8870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>0</v>
       </c>
@@ -8860,7 +8899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>0</v>
       </c>
@@ -8889,7 +8928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>0</v>
       </c>
@@ -8918,7 +8957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0</v>
       </c>
@@ -8947,7 +8986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>0</v>
       </c>
@@ -8976,7 +9015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>0</v>
       </c>
@@ -9005,7 +9044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>0</v>
       </c>
@@ -9034,7 +9073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>0</v>
       </c>
@@ -9063,7 +9102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>0</v>
       </c>
@@ -9092,7 +9131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>0</v>
       </c>
@@ -9121,7 +9160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>0</v>
       </c>
@@ -9150,7 +9189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>0</v>
       </c>
@@ -9179,7 +9218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>0</v>
       </c>
@@ -9208,7 +9247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>0</v>
       </c>
@@ -9237,7 +9276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>0</v>
       </c>
@@ -9266,7 +9305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>0</v>
       </c>
@@ -9295,7 +9334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>0</v>
       </c>
@@ -9324,7 +9363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>0</v>
       </c>
@@ -9353,12 +9392,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>0</v>
       </c>
@@ -9387,7 +9426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>0</v>
       </c>
@@ -9416,7 +9455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>0</v>
       </c>
@@ -9445,7 +9484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>0</v>
       </c>
@@ -9474,7 +9513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>0</v>
       </c>
@@ -9503,7 +9542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>0</v>
       </c>
@@ -9532,7 +9571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>0</v>
       </c>
@@ -9561,7 +9600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>0</v>
       </c>
@@ -9590,7 +9629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>0</v>
       </c>
@@ -9619,7 +9658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>0</v>
       </c>
@@ -9648,7 +9687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>1</v>
       </c>
@@ -9677,7 +9716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>0</v>
       </c>
@@ -9706,7 +9745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>0</v>
       </c>
@@ -9735,7 +9774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>0</v>
       </c>
@@ -9764,7 +9803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>0</v>
       </c>
@@ -9793,7 +9832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>0</v>
       </c>
@@ -9822,7 +9861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>0</v>
       </c>
@@ -9851,7 +9890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>0</v>
       </c>
@@ -9880,7 +9919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>0</v>
       </c>
@@ -9909,7 +9948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>1</v>
       </c>
@@ -9938,7 +9977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>0</v>
       </c>
@@ -9967,7 +10006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>0</v>
       </c>
@@ -9996,7 +10035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>0</v>
       </c>
@@ -10025,12 +10064,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>0</v>
       </c>
@@ -10059,7 +10098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>0</v>
       </c>
@@ -10088,7 +10127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>0</v>
       </c>
@@ -10117,7 +10156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>0</v>
       </c>
@@ -10146,7 +10185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>2.5</v>
       </c>
@@ -10175,7 +10214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>2.5</v>
       </c>
@@ -10204,7 +10243,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>2.5</v>
       </c>
@@ -10233,7 +10272,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>0.73</v>
       </c>
@@ -10262,7 +10301,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>1.3</v>
       </c>
@@ -10291,7 +10330,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>1.3</v>
       </c>
@@ -10320,7 +10359,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>0</v>
       </c>
@@ -10349,7 +10388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>0</v>
       </c>
@@ -10378,7 +10417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>0</v>
       </c>
@@ -10407,7 +10446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>0</v>
       </c>
@@ -10436,7 +10475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>0</v>
       </c>
@@ -10465,7 +10504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>0</v>
       </c>
@@ -10494,7 +10533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>2.5</v>
       </c>
@@ -10523,7 +10562,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>2.5</v>
       </c>
@@ -10552,7 +10591,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>0</v>
       </c>
@@ -10581,7 +10620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>0</v>
       </c>
@@ -10610,7 +10649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>0</v>
       </c>
@@ -10639,7 +10678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>0</v>
       </c>
@@ -10668,7 +10707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>0</v>
       </c>
@@ -10697,12 +10736,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>191000000000000</v>
       </c>
@@ -10713,7 +10752,7 @@
         <v>16440</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>50800</v>
       </c>
@@ -10727,7 +10766,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>216000000</v>
       </c>
@@ -10741,7 +10780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>2970000</v>
       </c>
@@ -10752,7 +10791,7 @@
         <v>13400</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>37</v>
       </c>
@@ -10761,7 +10800,7 @@
       </c>
       <c r="C80" s="4"/>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>38</v>
       </c>
@@ -10772,7 +10811,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>39</v>
       </c>
@@ -10783,7 +10822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>40</v>
       </c>
@@ -10794,7 +10833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>41</v>
       </c>
@@ -10803,7 +10842,7 @@
       </c>
       <c r="C84" s="4"/>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>1480000000000</v>
       </c>
@@ -10817,7 +10856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>16600000000000</v>
       </c>
@@ -10831,7 +10870,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>70800000000000</v>
       </c>
@@ -10845,7 +10884,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>32500000000000</v>
       </c>
@@ -10859,7 +10898,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>28900000000000</v>
       </c>
@@ -10873,7 +10912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>420000000000000</v>
       </c>
@@ -10884,7 +10923,7 @@
         <v>11980</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>130000000000</v>
       </c>
@@ -10895,7 +10934,7 @@
         <v>-1629</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>1.27E+17</v>
       </c>
@@ -10906,7 +10945,7 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>295000000000000</v>
       </c>
@@ -10917,7 +10956,7 @@
         <v>48400</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>24100000000000</v>
       </c>
@@ -10931,7 +10970,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>60300000000000</v>
       </c>
@@ -10945,7 +10984,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>9550000</v>
       </c>
@@ -10956,7 +10995,7 @@
         <v>3970</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>1000000000000</v>
       </c>
@@ -10970,7 +11009,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>580000000000000</v>
       </c>
@@ -10981,6 +11020,2168 @@
         <v>9560</v>
       </c>
       <c r="D98" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CD23AF9-4AAA-476C-A75B-6CE20E16E2E9}">
+  <dimension ref="A1:V84"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="9" width="10.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" style="7" customWidth="1"/>
+    <col min="11" max="19" width="5.77734375" customWidth="1"/>
+    <col min="20" max="22" width="10.77734375" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="8"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7</v>
+      </c>
+      <c r="J2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7</v>
+      </c>
+      <c r="J3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+    </row>
+    <row r="4" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>0</v>
+      </c>
+      <c r="B6" s="9">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>1</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>1</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="11"/>
+    </row>
+    <row r="9" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>0</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>0</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11"/>
+    </row>
+    <row r="11" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>0</v>
+      </c>
+      <c r="B11" s="9">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0</v>
+      </c>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>0</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
+        <v>0</v>
+      </c>
+      <c r="B13" s="9">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>0</v>
+      </c>
+      <c r="B14" s="9">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>1</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>0</v>
+      </c>
+      <c r="B15" s="9">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
+        <v>1</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
+        <v>0</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>0</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9">
+        <v>0</v>
+      </c>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>0</v>
+      </c>
+      <c r="B18" s="9">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>2</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="11"/>
+    </row>
+    <row r="19" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>0</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>1</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>1</v>
+      </c>
+      <c r="H19" s="9">
+        <v>0</v>
+      </c>
+      <c r="I19" s="9">
+        <v>0</v>
+      </c>
+      <c r="J19" s="11"/>
+    </row>
+    <row r="20" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>0</v>
+      </c>
+      <c r="B20" s="9">
+        <v>0</v>
+      </c>
+      <c r="C20" s="9">
+        <v>1</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>1</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="11"/>
+    </row>
+    <row r="21" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>0</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9">
+        <v>0</v>
+      </c>
+      <c r="J21" s="11"/>
+    </row>
+    <row r="22" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
+        <v>0</v>
+      </c>
+      <c r="B22" s="9">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>1</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>0</v>
+      </c>
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>0</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9">
+        <v>2</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>0</v>
+      </c>
+      <c r="I23" s="9">
+        <v>0</v>
+      </c>
+      <c r="J23" s="11"/>
+    </row>
+    <row r="24" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+    </row>
+    <row r="25" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>0</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0</v>
+      </c>
+      <c r="D25" s="9">
+        <v>1</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9">
+        <v>1</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0</v>
+      </c>
+      <c r="I25" s="9">
+        <v>0</v>
+      </c>
+      <c r="J25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+    </row>
+    <row r="26" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>0</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0</v>
+      </c>
+      <c r="J26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="11"/>
+    </row>
+    <row r="27" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>0</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
+        <v>1</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0</v>
+      </c>
+      <c r="J27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="11"/>
+      <c r="V27" s="11"/>
+    </row>
+    <row r="28" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>0</v>
+      </c>
+      <c r="B28" s="9">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>1</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>1</v>
+      </c>
+      <c r="I28" s="9">
+        <v>0</v>
+      </c>
+      <c r="J28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="11"/>
+      <c r="V28" s="11"/>
+    </row>
+    <row r="29" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>0</v>
+      </c>
+      <c r="B29" s="9">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9">
+        <v>1</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>1</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0</v>
+      </c>
+      <c r="J29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
+    </row>
+    <row r="30" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>0</v>
+      </c>
+      <c r="B30" s="9">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>1</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
+      <c r="J30" s="11"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="11"/>
+    </row>
+    <row r="31" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
+        <v>1</v>
+      </c>
+      <c r="B31" s="9">
+        <v>0</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>0</v>
+      </c>
+      <c r="I31" s="9">
+        <v>0</v>
+      </c>
+      <c r="J31" s="11"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="11"/>
+      <c r="V31" s="11"/>
+    </row>
+    <row r="32" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9">
+        <v>0</v>
+      </c>
+      <c r="B32" s="9">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <v>1</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9">
+        <v>0</v>
+      </c>
+      <c r="J32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11"/>
+      <c r="V32" s="11"/>
+    </row>
+    <row r="33" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9">
+        <v>0</v>
+      </c>
+      <c r="B33" s="9">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9">
+        <v>1</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9">
+        <v>0</v>
+      </c>
+      <c r="I33" s="9">
+        <v>0</v>
+      </c>
+      <c r="J33" s="11"/>
+      <c r="T33" s="11"/>
+      <c r="U33" s="11"/>
+      <c r="V33" s="11"/>
+    </row>
+    <row r="34" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9">
+        <v>0</v>
+      </c>
+      <c r="B34" s="9">
+        <v>0</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
+        <v>2</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="9">
+        <v>0</v>
+      </c>
+      <c r="J34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="11"/>
+      <c r="V34" s="11"/>
+    </row>
+    <row r="35" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="9">
+        <v>0</v>
+      </c>
+      <c r="B35" s="9">
+        <v>0</v>
+      </c>
+      <c r="C35" s="9">
+        <v>1</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9">
+        <v>0</v>
+      </c>
+      <c r="G35" s="9">
+        <v>0</v>
+      </c>
+      <c r="H35" s="9">
+        <v>1</v>
+      </c>
+      <c r="I35" s="9">
+        <v>0</v>
+      </c>
+      <c r="J35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="11"/>
+      <c r="V35" s="11"/>
+    </row>
+    <row r="36" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="9">
+        <v>0</v>
+      </c>
+      <c r="B36" s="9">
+        <v>1</v>
+      </c>
+      <c r="C36" s="9">
+        <v>0</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9">
+        <v>1</v>
+      </c>
+      <c r="F36" s="9">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0</v>
+      </c>
+      <c r="H36" s="9">
+        <v>0</v>
+      </c>
+      <c r="I36" s="9">
+        <v>0</v>
+      </c>
+      <c r="J36" s="11"/>
+      <c r="T36" s="11"/>
+      <c r="U36" s="11"/>
+      <c r="V36" s="11"/>
+    </row>
+    <row r="37" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9">
+        <v>0</v>
+      </c>
+      <c r="B37" s="9">
+        <v>1</v>
+      </c>
+      <c r="C37" s="9">
+        <v>0</v>
+      </c>
+      <c r="D37" s="9">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9">
+        <v>0</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0</v>
+      </c>
+      <c r="H37" s="9">
+        <v>1</v>
+      </c>
+      <c r="I37" s="9">
+        <v>0</v>
+      </c>
+      <c r="J37" s="11"/>
+      <c r="T37" s="11"/>
+      <c r="U37" s="11"/>
+      <c r="V37" s="11"/>
+    </row>
+    <row r="38" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="9">
+        <v>0</v>
+      </c>
+      <c r="B38" s="9">
+        <v>1</v>
+      </c>
+      <c r="C38" s="9">
+        <v>0</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>1</v>
+      </c>
+      <c r="H38" s="9">
+        <v>0</v>
+      </c>
+      <c r="I38" s="9">
+        <v>0</v>
+      </c>
+      <c r="J38" s="11"/>
+      <c r="T38" s="11"/>
+      <c r="U38" s="11"/>
+      <c r="V38" s="11"/>
+    </row>
+    <row r="39" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9">
+        <v>1</v>
+      </c>
+      <c r="B39" s="9">
+        <v>0</v>
+      </c>
+      <c r="C39" s="9">
+        <v>0</v>
+      </c>
+      <c r="D39" s="9">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9">
+        <v>0</v>
+      </c>
+      <c r="I39" s="9">
+        <v>0</v>
+      </c>
+      <c r="J39" s="11"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="11"/>
+      <c r="V39" s="11"/>
+    </row>
+    <row r="40" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="9">
+        <v>0</v>
+      </c>
+      <c r="B40" s="9">
+        <v>0</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0</v>
+      </c>
+      <c r="D40" s="9">
+        <v>0</v>
+      </c>
+      <c r="E40" s="9">
+        <v>1</v>
+      </c>
+      <c r="F40" s="9">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>0</v>
+      </c>
+      <c r="I40" s="9">
+        <v>0</v>
+      </c>
+      <c r="J40" s="11"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="11"/>
+      <c r="V40" s="11"/>
+    </row>
+    <row r="41" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="9">
+        <v>0</v>
+      </c>
+      <c r="B41" s="9">
+        <v>0</v>
+      </c>
+      <c r="C41" s="9">
+        <v>0</v>
+      </c>
+      <c r="D41" s="9">
+        <v>0</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9">
+        <v>1</v>
+      </c>
+      <c r="G41" s="9">
+        <v>0</v>
+      </c>
+      <c r="H41" s="9">
+        <v>1</v>
+      </c>
+      <c r="I41" s="9">
+        <v>0</v>
+      </c>
+      <c r="J41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="11"/>
+      <c r="V41" s="11"/>
+    </row>
+    <row r="42" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="9">
+        <v>0</v>
+      </c>
+      <c r="B42" s="9">
+        <v>0</v>
+      </c>
+      <c r="C42" s="9">
+        <v>0</v>
+      </c>
+      <c r="D42" s="9">
+        <v>0</v>
+      </c>
+      <c r="E42" s="9">
+        <v>2</v>
+      </c>
+      <c r="F42" s="9">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9">
+        <v>0</v>
+      </c>
+      <c r="H42" s="9">
+        <v>0</v>
+      </c>
+      <c r="I42" s="9">
+        <v>0</v>
+      </c>
+      <c r="J42" s="11"/>
+      <c r="T42" s="11"/>
+      <c r="U42" s="11"/>
+      <c r="V42" s="11"/>
+    </row>
+    <row r="43" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="9">
+        <v>0</v>
+      </c>
+      <c r="B43" s="9">
+        <v>1</v>
+      </c>
+      <c r="C43" s="9">
+        <v>0</v>
+      </c>
+      <c r="D43" s="9">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9">
+        <v>0</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0</v>
+      </c>
+      <c r="H43" s="9">
+        <v>0</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0</v>
+      </c>
+      <c r="J43" s="11"/>
+      <c r="T43" s="11"/>
+      <c r="U43" s="11"/>
+      <c r="V43" s="11"/>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45" s="9">
+        <v>0</v>
+      </c>
+      <c r="B45" s="9">
+        <v>0</v>
+      </c>
+      <c r="C45" s="9">
+        <v>0</v>
+      </c>
+      <c r="D45" s="9">
+        <v>0</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9">
+        <v>0</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0</v>
+      </c>
+      <c r="H45" s="9">
+        <v>0</v>
+      </c>
+      <c r="I45" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" s="9">
+        <v>0</v>
+      </c>
+      <c r="B46" s="9">
+        <v>0</v>
+      </c>
+      <c r="C46" s="9">
+        <v>0</v>
+      </c>
+      <c r="D46" s="9">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>0</v>
+      </c>
+      <c r="I46" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" s="9">
+        <v>0</v>
+      </c>
+      <c r="B47" s="9">
+        <v>0</v>
+      </c>
+      <c r="C47" s="9">
+        <v>0</v>
+      </c>
+      <c r="D47" s="9">
+        <v>0</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>0</v>
+      </c>
+      <c r="I47" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" s="9">
+        <v>0</v>
+      </c>
+      <c r="B48" s="9">
+        <v>0</v>
+      </c>
+      <c r="C48" s="9">
+        <v>0</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>0</v>
+      </c>
+      <c r="I48" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="9">
+        <v>0</v>
+      </c>
+      <c r="B49" s="9">
+        <v>0</v>
+      </c>
+      <c r="C49" s="9">
+        <v>0</v>
+      </c>
+      <c r="D49" s="9">
+        <v>0</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>0</v>
+      </c>
+      <c r="I49" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="9">
+        <v>1</v>
+      </c>
+      <c r="B50" s="9">
+        <v>1</v>
+      </c>
+      <c r="C50" s="9">
+        <v>1</v>
+      </c>
+      <c r="D50" s="9">
+        <v>1</v>
+      </c>
+      <c r="E50" s="9">
+        <v>1</v>
+      </c>
+      <c r="F50" s="9">
+        <v>1</v>
+      </c>
+      <c r="G50" s="9">
+        <v>1</v>
+      </c>
+      <c r="H50" s="9">
+        <v>6</v>
+      </c>
+      <c r="I50" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="9">
+        <v>2</v>
+      </c>
+      <c r="B51" s="9">
+        <v>1</v>
+      </c>
+      <c r="C51" s="9">
+        <v>1</v>
+      </c>
+      <c r="D51" s="9">
+        <v>1</v>
+      </c>
+      <c r="E51" s="9">
+        <v>1</v>
+      </c>
+      <c r="F51" s="9">
+        <v>1</v>
+      </c>
+      <c r="G51" s="9">
+        <v>1</v>
+      </c>
+      <c r="H51" s="9">
+        <v>6</v>
+      </c>
+      <c r="I51" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="9">
+        <v>1</v>
+      </c>
+      <c r="B52" s="9">
+        <v>1</v>
+      </c>
+      <c r="C52" s="9">
+        <v>1</v>
+      </c>
+      <c r="D52" s="9">
+        <v>1</v>
+      </c>
+      <c r="E52" s="9">
+        <v>1</v>
+      </c>
+      <c r="F52" s="9">
+        <v>1</v>
+      </c>
+      <c r="G52" s="9">
+        <v>1</v>
+      </c>
+      <c r="H52" s="9">
+        <v>6</v>
+      </c>
+      <c r="I52" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="9">
+        <v>2</v>
+      </c>
+      <c r="B53" s="9">
+        <v>1</v>
+      </c>
+      <c r="C53" s="9">
+        <v>1</v>
+      </c>
+      <c r="D53" s="9">
+        <v>1</v>
+      </c>
+      <c r="E53" s="9">
+        <v>1</v>
+      </c>
+      <c r="F53" s="9">
+        <v>1</v>
+      </c>
+      <c r="G53" s="9">
+        <v>1</v>
+      </c>
+      <c r="H53" s="9">
+        <v>6</v>
+      </c>
+      <c r="I53" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="9">
+        <v>0</v>
+      </c>
+      <c r="B54" s="9">
+        <v>0</v>
+      </c>
+      <c r="C54" s="9">
+        <v>0</v>
+      </c>
+      <c r="D54" s="9">
+        <v>0</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>0</v>
+      </c>
+      <c r="I54" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="9">
+        <v>0</v>
+      </c>
+      <c r="B55" s="9">
+        <v>0</v>
+      </c>
+      <c r="C55" s="9">
+        <v>0</v>
+      </c>
+      <c r="D55" s="9">
+        <v>0</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0</v>
+      </c>
+      <c r="F55" s="9">
+        <v>0</v>
+      </c>
+      <c r="G55" s="9">
+        <v>0</v>
+      </c>
+      <c r="H55" s="9">
+        <v>0</v>
+      </c>
+      <c r="I55" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="9">
+        <v>0</v>
+      </c>
+      <c r="B56" s="9">
+        <v>0</v>
+      </c>
+      <c r="C56" s="9">
+        <v>0</v>
+      </c>
+      <c r="D56" s="9">
+        <v>0</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0</v>
+      </c>
+      <c r="F56" s="9">
+        <v>0</v>
+      </c>
+      <c r="G56" s="9">
+        <v>0</v>
+      </c>
+      <c r="H56" s="9">
+        <v>0</v>
+      </c>
+      <c r="I56" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="9">
+        <v>0</v>
+      </c>
+      <c r="B57" s="9">
+        <v>0</v>
+      </c>
+      <c r="C57" s="9">
+        <v>0</v>
+      </c>
+      <c r="D57" s="9">
+        <v>0</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0</v>
+      </c>
+      <c r="F57" s="9">
+        <v>0</v>
+      </c>
+      <c r="G57" s="9">
+        <v>0</v>
+      </c>
+      <c r="H57" s="9">
+        <v>0</v>
+      </c>
+      <c r="I57" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="9">
+        <v>0</v>
+      </c>
+      <c r="B58" s="9">
+        <v>0</v>
+      </c>
+      <c r="C58" s="9">
+        <v>0</v>
+      </c>
+      <c r="D58" s="9">
+        <v>0</v>
+      </c>
+      <c r="E58" s="9">
+        <v>0</v>
+      </c>
+      <c r="F58" s="9">
+        <v>0</v>
+      </c>
+      <c r="G58" s="9">
+        <v>0</v>
+      </c>
+      <c r="H58" s="9">
+        <v>0</v>
+      </c>
+      <c r="I58" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="9">
+        <v>0</v>
+      </c>
+      <c r="B59" s="9">
+        <v>0</v>
+      </c>
+      <c r="C59" s="9">
+        <v>0</v>
+      </c>
+      <c r="D59" s="9">
+        <v>0</v>
+      </c>
+      <c r="E59" s="9">
+        <v>0</v>
+      </c>
+      <c r="F59" s="9">
+        <v>0</v>
+      </c>
+      <c r="G59" s="9">
+        <v>0</v>
+      </c>
+      <c r="H59" s="9">
+        <v>0</v>
+      </c>
+      <c r="I59" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="9">
+        <v>0</v>
+      </c>
+      <c r="B60" s="9">
+        <v>0</v>
+      </c>
+      <c r="C60" s="9">
+        <v>0</v>
+      </c>
+      <c r="D60" s="9">
+        <v>0</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0</v>
+      </c>
+      <c r="F60" s="9">
+        <v>0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9">
+        <v>0</v>
+      </c>
+      <c r="I60" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="9">
+        <v>0</v>
+      </c>
+      <c r="B61" s="9">
+        <v>0</v>
+      </c>
+      <c r="C61" s="9">
+        <v>0</v>
+      </c>
+      <c r="D61" s="9">
+        <v>0</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0</v>
+      </c>
+      <c r="F61" s="9">
+        <v>0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9">
+        <v>0</v>
+      </c>
+      <c r="I61" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="9">
+        <v>1</v>
+      </c>
+      <c r="B62" s="9">
+        <v>1</v>
+      </c>
+      <c r="C62" s="9">
+        <v>1</v>
+      </c>
+      <c r="D62" s="9">
+        <v>1</v>
+      </c>
+      <c r="E62" s="9">
+        <v>1</v>
+      </c>
+      <c r="F62" s="9">
+        <v>1</v>
+      </c>
+      <c r="G62" s="9">
+        <v>1</v>
+      </c>
+      <c r="H62" s="9">
+        <v>15</v>
+      </c>
+      <c r="I62" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="9">
+        <v>1</v>
+      </c>
+      <c r="B63" s="9">
+        <v>1</v>
+      </c>
+      <c r="C63" s="9">
+        <v>1</v>
+      </c>
+      <c r="D63" s="9">
+        <v>1</v>
+      </c>
+      <c r="E63" s="9">
+        <v>1</v>
+      </c>
+      <c r="F63" s="9">
+        <v>1</v>
+      </c>
+      <c r="G63" s="9">
+        <v>1</v>
+      </c>
+      <c r="H63" s="9">
+        <v>1</v>
+      </c>
+      <c r="I63" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <v>100000000000</v>
+      </c>
+      <c r="B65" s="13">
+        <v>0</v>
+      </c>
+      <c r="C65" s="13">
+        <v>56000</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <v>260000000000</v>
+      </c>
+      <c r="B66" s="13">
+        <v>0</v>
+      </c>
+      <c r="C66" s="13">
+        <v>16800</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <v>18000000</v>
+      </c>
+      <c r="B67" s="13">
+        <v>1</v>
+      </c>
+      <c r="C67" s="13">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <v>22000000000</v>
+      </c>
+      <c r="B68" s="13">
+        <v>0</v>
+      </c>
+      <c r="C68" s="13">
+        <v>5150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <v>6300000000</v>
+      </c>
+      <c r="B69" s="9">
+        <v>0</v>
+      </c>
+      <c r="C69" s="13">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <v>2.2E+16</v>
+      </c>
+      <c r="B70" s="9">
+        <v>-2</v>
+      </c>
+      <c r="C70" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <v>640000000000</v>
+      </c>
+      <c r="B71" s="9">
+        <v>-1</v>
+      </c>
+      <c r="C71" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <v>60000000000</v>
+      </c>
+      <c r="B72" s="9">
+        <v>-0.6</v>
+      </c>
+      <c r="C72" s="13">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="12">
+        <v>2100000000</v>
+      </c>
+      <c r="B73" s="13">
+        <v>0</v>
+      </c>
+      <c r="C73" s="13">
+        <v>-1000</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <v>140000000000</v>
+      </c>
+      <c r="B74" s="13">
+        <v>0</v>
+      </c>
+      <c r="C74" s="13">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <v>10000000000</v>
+      </c>
+      <c r="B75" s="13">
+        <v>0</v>
+      </c>
+      <c r="C75" s="13">
+        <v>1080</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <v>15000000000</v>
+      </c>
+      <c r="B76" s="13">
+        <v>0</v>
+      </c>
+      <c r="C76" s="13">
+        <v>950</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="12">
+        <v>8000000000</v>
+      </c>
+      <c r="B77" s="9">
+        <v>0</v>
+      </c>
+      <c r="C77" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
+        <v>2000000000</v>
+      </c>
+      <c r="B78" s="9">
+        <v>0</v>
+      </c>
+      <c r="C78" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="12">
+        <v>1400000000</v>
+      </c>
+      <c r="B79" s="13">
+        <v>0</v>
+      </c>
+      <c r="C79" s="13">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <v>14000000000</v>
+      </c>
+      <c r="B80" s="13">
+        <v>0</v>
+      </c>
+      <c r="C80" s="13">
+        <v>6400</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <v>6100000000</v>
+      </c>
+      <c r="B81" s="13">
+        <v>0</v>
+      </c>
+      <c r="C81" s="13">
+        <v>1430</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <v>120000000000000</v>
+      </c>
+      <c r="B82" s="13">
+        <v>0</v>
+      </c>
+      <c r="C82" s="13">
+        <v>45500</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <v>60000000</v>
+      </c>
+      <c r="B83" s="13">
+        <v>0</v>
+      </c>
+      <c r="C83" s="13">
+        <v>-1800</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D84" s="2" t="s">
         <v>13</v>
       </c>
     </row>

--- a/runtime.dat/Reaction/Reactions.xlsx
+++ b/runtime.dat/Reaction/Reactions.xlsx
@@ -5,26 +5,29 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\XFLUIDS\runtime.dat\Reaction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\XFLUIDS\runtime.dat\Reaction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1641575A-BE5B-4103-9AD1-0D6CD0F755E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAEA338-698E-48DE-9E5A-58B9D22A3F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="H2O_18_Reaction" sheetId="4" r:id="rId1"/>
-    <sheet name="H2O_19_Reaction" sheetId="1" r:id="rId2"/>
-    <sheet name="H2O_21_Reaction" sheetId="2" r:id="rId3"/>
+    <sheet name="N2" sheetId="8" r:id="rId1"/>
+    <sheet name="H2O_18_Reaction" sheetId="4" r:id="rId2"/>
+    <sheet name="H2O_19_Reaction" sheetId="1" r:id="rId3"/>
     <sheet name="H2O_23_Reaction" sheetId="3" r:id="rId4"/>
-    <sheet name="H2O-N2_19_Reaction" sheetId="5" r:id="rId5"/>
+    <sheet name="H2O-N2_16_Reaction" sheetId="7" r:id="rId5"/>
+    <sheet name="H2O-N2_19_Reaction" sheetId="5" r:id="rId6"/>
+    <sheet name="H2O-N2_21_Reaction" sheetId="2" r:id="rId7"/>
+    <sheet name="H2O-N2_25_Reaction" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="50">
   <si>
     <t xml:space="preserve">H2    </t>
   </si>
@@ -152,13 +155,48 @@
   <si>
     <t>3.48E+16   -0.41</t>
   </si>
+  <si>
+    <t>3..486E-16</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.14*T^(0.4)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>93.8*T^(-0.25)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>4*T^(-0.06)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>429*T^(-0.92)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.4*T^(0.04)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>536*T^(-0.92)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.000E+00"/>
+    <numFmt numFmtId="178" formatCode="0.000_ "/>
+    <numFmt numFmtId="179" formatCode="0.0000E+00"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -763,7 +801,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -804,6 +842,36 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1160,6 +1228,118 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467D511C-DDD0-4E20-A8A4-4AE18809BD9F}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>3.7E+21</v>
+      </c>
+      <c r="B13">
+        <v>-1.6</v>
+      </c>
+      <c r="C13">
+        <v>113200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>1.66E+22</v>
+      </c>
+      <c r="B14">
+        <v>-1.6</v>
+      </c>
+      <c r="C14">
+        <v>113200</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5977D6-625A-4B51-AC0B-2BFDB941363F}">
   <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -3276,7 +3456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J98"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -5858,2791 +6038,6 @@
       </c>
       <c r="E98" t="s">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I113"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="8.88671875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>0</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>0</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>0</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>0</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>0</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>0</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>0</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>0</v>
-      </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>0</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>0</v>
-      </c>
-      <c r="B17" s="2">
-        <v>1</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>0</v>
-      </c>
-      <c r="B18" s="2">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>0</v>
-      </c>
-      <c r="B19" s="2">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>0</v>
-      </c>
-      <c r="B20" s="2">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>0</v>
-      </c>
-      <c r="B21" s="2">
-        <v>0</v>
-      </c>
-      <c r="C21" s="2">
-        <v>0</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>0</v>
-      </c>
-      <c r="B22" s="2">
-        <v>0</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>0</v>
-      </c>
-      <c r="B23" s="2">
-        <v>0</v>
-      </c>
-      <c r="C23" s="2">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>0</v>
-      </c>
-      <c r="B24" s="2">
-        <v>0</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>0</v>
-      </c>
-      <c r="B26" s="2">
-        <v>0</v>
-      </c>
-      <c r="C26" s="2">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>0</v>
-      </c>
-      <c r="B27" s="2">
-        <v>0</v>
-      </c>
-      <c r="C27" s="2">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1</v>
-      </c>
-      <c r="E27" s="2">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>0</v>
-      </c>
-      <c r="B28" s="2">
-        <v>0</v>
-      </c>
-      <c r="C28" s="2">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
-        <v>1</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>0</v>
-      </c>
-      <c r="B29" s="2">
-        <v>0</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2">
-        <v>2</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>0</v>
-      </c>
-      <c r="B30" s="2">
-        <v>0</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2">
-        <v>2</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>0</v>
-      </c>
-      <c r="B31" s="2">
-        <v>0</v>
-      </c>
-      <c r="C31" s="2">
-        <v>2</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>0</v>
-      </c>
-      <c r="B32" s="2">
-        <v>0</v>
-      </c>
-      <c r="C32" s="2">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2">
-        <v>1</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>0</v>
-      </c>
-      <c r="B33" s="2">
-        <v>0</v>
-      </c>
-      <c r="C33" s="2">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2">
-        <v>1</v>
-      </c>
-      <c r="E33" s="2">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2">
-        <v>0</v>
-      </c>
-      <c r="H33" s="2">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>0</v>
-      </c>
-      <c r="B34" s="2">
-        <v>0</v>
-      </c>
-      <c r="C34" s="2">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>1</v>
-      </c>
-      <c r="B35" s="2">
-        <v>1</v>
-      </c>
-      <c r="C35" s="2">
-        <v>0</v>
-      </c>
-      <c r="D35" s="2">
-        <v>0</v>
-      </c>
-      <c r="E35" s="2">
-        <v>0</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>0</v>
-      </c>
-      <c r="B36" s="2">
-        <v>0</v>
-      </c>
-      <c r="C36" s="2">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2">
-        <v>2</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>0</v>
-      </c>
-      <c r="B37" s="2">
-        <v>1</v>
-      </c>
-      <c r="C37" s="2">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2">
-        <v>0</v>
-      </c>
-      <c r="E37" s="2">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>0</v>
-      </c>
-      <c r="B38" s="2">
-        <v>1</v>
-      </c>
-      <c r="C38" s="2">
-        <v>0</v>
-      </c>
-      <c r="D38" s="2">
-        <v>0</v>
-      </c>
-      <c r="E38" s="2">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2">
-        <v>1</v>
-      </c>
-      <c r="I38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>0</v>
-      </c>
-      <c r="B39" s="2">
-        <v>0</v>
-      </c>
-      <c r="C39" s="2">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
-        <v>2</v>
-      </c>
-      <c r="G39" s="2">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>0</v>
-      </c>
-      <c r="B40" s="2">
-        <v>0</v>
-      </c>
-      <c r="C40" s="2">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2">
-        <v>2</v>
-      </c>
-      <c r="G40" s="2">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2">
-        <v>0</v>
-      </c>
-      <c r="I40" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>0</v>
-      </c>
-      <c r="B41" s="2">
-        <v>0</v>
-      </c>
-      <c r="C41" s="2">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2">
-        <v>2</v>
-      </c>
-      <c r="F41" s="2">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2">
-        <v>0</v>
-      </c>
-      <c r="I41" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>0</v>
-      </c>
-      <c r="B42" s="2">
-        <v>0</v>
-      </c>
-      <c r="C42" s="2">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2">
-        <v>1</v>
-      </c>
-      <c r="I42" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>1</v>
-      </c>
-      <c r="B43" s="2">
-        <v>0</v>
-      </c>
-      <c r="C43" s="2">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
-        <v>1</v>
-      </c>
-      <c r="G43" s="2">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>0</v>
-      </c>
-      <c r="B44" s="2">
-        <v>0</v>
-      </c>
-      <c r="C44" s="2">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>0</v>
-      </c>
-      <c r="B45" s="2">
-        <v>0</v>
-      </c>
-      <c r="C45" s="2">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2">
-        <v>1</v>
-      </c>
-      <c r="G45" s="2">
-        <v>0</v>
-      </c>
-      <c r="H45" s="2">
-        <v>1</v>
-      </c>
-      <c r="I45" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>0</v>
-      </c>
-      <c r="B46" s="2">
-        <v>0</v>
-      </c>
-      <c r="C46" s="2">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2">
-        <v>1</v>
-      </c>
-      <c r="G46" s="2">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2">
-        <v>1</v>
-      </c>
-      <c r="I46" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>0</v>
-      </c>
-      <c r="B48" s="2">
-        <v>0</v>
-      </c>
-      <c r="C48" s="2">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>0</v>
-      </c>
-      <c r="B49" s="2">
-        <v>0</v>
-      </c>
-      <c r="C49" s="2">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>0</v>
-      </c>
-      <c r="B50" s="2">
-        <v>0</v>
-      </c>
-      <c r="C50" s="2">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2">
-        <v>0</v>
-      </c>
-      <c r="E50" s="2">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>0</v>
-      </c>
-      <c r="B51" s="2">
-        <v>0</v>
-      </c>
-      <c r="C51" s="2">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2">
-        <v>0</v>
-      </c>
-      <c r="E51" s="2">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2">
-        <v>0</v>
-      </c>
-      <c r="G51" s="2">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="B52" s="2">
-        <v>1</v>
-      </c>
-      <c r="C52" s="2">
-        <v>1</v>
-      </c>
-      <c r="D52" s="2">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2">
-        <v>1</v>
-      </c>
-      <c r="F52" s="2">
-        <v>1</v>
-      </c>
-      <c r="G52" s="2">
-        <v>1</v>
-      </c>
-      <c r="H52" s="2">
-        <v>12</v>
-      </c>
-      <c r="I52" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="B53" s="2">
-        <v>1</v>
-      </c>
-      <c r="C53" s="2">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2">
-        <v>1</v>
-      </c>
-      <c r="E53" s="2">
-        <v>1</v>
-      </c>
-      <c r="F53" s="2">
-        <v>1</v>
-      </c>
-      <c r="G53" s="2">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2">
-        <v>12</v>
-      </c>
-      <c r="I53" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="B54" s="2">
-        <v>1</v>
-      </c>
-      <c r="C54" s="2">
-        <v>1</v>
-      </c>
-      <c r="D54" s="2">
-        <v>1</v>
-      </c>
-      <c r="E54" s="2">
-        <v>1</v>
-      </c>
-      <c r="F54" s="2">
-        <v>1</v>
-      </c>
-      <c r="G54" s="2">
-        <v>1</v>
-      </c>
-      <c r="H54" s="2">
-        <v>12</v>
-      </c>
-      <c r="I54" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>0.73</v>
-      </c>
-      <c r="B55" s="2">
-        <v>1</v>
-      </c>
-      <c r="C55" s="2">
-        <v>1</v>
-      </c>
-      <c r="D55" s="2">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2">
-        <v>1</v>
-      </c>
-      <c r="F55" s="2">
-        <v>1</v>
-      </c>
-      <c r="G55" s="2">
-        <v>1</v>
-      </c>
-      <c r="H55" s="2">
-        <v>12</v>
-      </c>
-      <c r="I55" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="B56" s="2">
-        <v>1</v>
-      </c>
-      <c r="C56" s="2">
-        <v>1</v>
-      </c>
-      <c r="D56" s="2">
-        <v>1</v>
-      </c>
-      <c r="E56" s="2">
-        <v>1</v>
-      </c>
-      <c r="F56" s="2">
-        <v>1</v>
-      </c>
-      <c r="G56" s="2">
-        <v>1</v>
-      </c>
-      <c r="H56" s="2">
-        <v>14</v>
-      </c>
-      <c r="I56" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>0</v>
-      </c>
-      <c r="B57" s="2">
-        <v>0</v>
-      </c>
-      <c r="C57" s="2">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2">
-        <v>0</v>
-      </c>
-      <c r="E57" s="2">
-        <v>0</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0</v>
-      </c>
-      <c r="G57" s="2">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2">
-        <v>0</v>
-      </c>
-      <c r="I57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>0</v>
-      </c>
-      <c r="B58" s="2">
-        <v>0</v>
-      </c>
-      <c r="C58" s="2">
-        <v>0</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
-      <c r="E58" s="2">
-        <v>0</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2">
-        <v>0</v>
-      </c>
-      <c r="H58" s="2">
-        <v>0</v>
-      </c>
-      <c r="I58" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>0</v>
-      </c>
-      <c r="B59" s="2">
-        <v>0</v>
-      </c>
-      <c r="C59" s="2">
-        <v>0</v>
-      </c>
-      <c r="D59" s="2">
-        <v>0</v>
-      </c>
-      <c r="E59" s="2">
-        <v>0</v>
-      </c>
-      <c r="F59" s="2">
-        <v>0</v>
-      </c>
-      <c r="G59" s="2">
-        <v>0</v>
-      </c>
-      <c r="H59" s="2">
-        <v>0</v>
-      </c>
-      <c r="I59" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>0</v>
-      </c>
-      <c r="B60" s="2">
-        <v>0</v>
-      </c>
-      <c r="C60" s="2">
-        <v>0</v>
-      </c>
-      <c r="D60" s="2">
-        <v>0</v>
-      </c>
-      <c r="E60" s="2">
-        <v>0</v>
-      </c>
-      <c r="F60" s="2">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>0</v>
-      </c>
-      <c r="B61" s="2">
-        <v>0</v>
-      </c>
-      <c r="C61" s="2">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2">
-        <v>0</v>
-      </c>
-      <c r="E61" s="2">
-        <v>0</v>
-      </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="2">
-        <v>0</v>
-      </c>
-      <c r="H61" s="2">
-        <v>0</v>
-      </c>
-      <c r="I61" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>0</v>
-      </c>
-      <c r="B62" s="2">
-        <v>0</v>
-      </c>
-      <c r="C62" s="2">
-        <v>0</v>
-      </c>
-      <c r="D62" s="2">
-        <v>0</v>
-      </c>
-      <c r="E62" s="2">
-        <v>0</v>
-      </c>
-      <c r="F62" s="2">
-        <v>0</v>
-      </c>
-      <c r="G62" s="2">
-        <v>0</v>
-      </c>
-      <c r="H62" s="2">
-        <v>0</v>
-      </c>
-      <c r="I62" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="B63" s="2">
-        <v>1</v>
-      </c>
-      <c r="C63" s="2">
-        <v>1</v>
-      </c>
-      <c r="D63" s="2">
-        <v>1</v>
-      </c>
-      <c r="E63" s="2">
-        <v>1</v>
-      </c>
-      <c r="F63" s="2">
-        <v>1</v>
-      </c>
-      <c r="G63" s="2">
-        <v>1</v>
-      </c>
-      <c r="H63" s="2">
-        <v>12</v>
-      </c>
-      <c r="I63" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
-        <v>0</v>
-      </c>
-      <c r="B64" s="2">
-        <v>0</v>
-      </c>
-      <c r="C64" s="2">
-        <v>0</v>
-      </c>
-      <c r="D64" s="2">
-        <v>0</v>
-      </c>
-      <c r="E64" s="2">
-        <v>0</v>
-      </c>
-      <c r="F64" s="2">
-        <v>0</v>
-      </c>
-      <c r="G64" s="2">
-        <v>0</v>
-      </c>
-      <c r="H64" s="2">
-        <v>0</v>
-      </c>
-      <c r="I64" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>0</v>
-      </c>
-      <c r="B65" s="2">
-        <v>0</v>
-      </c>
-      <c r="C65" s="2">
-        <v>0</v>
-      </c>
-      <c r="D65" s="2">
-        <v>0</v>
-      </c>
-      <c r="E65" s="2">
-        <v>0</v>
-      </c>
-      <c r="F65" s="2">
-        <v>0</v>
-      </c>
-      <c r="G65" s="2">
-        <v>0</v>
-      </c>
-      <c r="H65" s="2">
-        <v>0</v>
-      </c>
-      <c r="I65" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>0</v>
-      </c>
-      <c r="B66" s="2">
-        <v>0</v>
-      </c>
-      <c r="C66" s="2">
-        <v>0</v>
-      </c>
-      <c r="D66" s="2">
-        <v>0</v>
-      </c>
-      <c r="E66" s="2">
-        <v>0</v>
-      </c>
-      <c r="F66" s="2">
-        <v>0</v>
-      </c>
-      <c r="G66" s="2">
-        <v>0</v>
-      </c>
-      <c r="H66" s="2">
-        <v>0</v>
-      </c>
-      <c r="I66" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>0</v>
-      </c>
-      <c r="B67" s="2">
-        <v>0</v>
-      </c>
-      <c r="C67" s="2">
-        <v>0</v>
-      </c>
-      <c r="D67" s="2">
-        <v>0</v>
-      </c>
-      <c r="E67" s="2">
-        <v>0</v>
-      </c>
-      <c r="F67" s="2">
-        <v>0</v>
-      </c>
-      <c r="G67" s="2">
-        <v>0</v>
-      </c>
-      <c r="H67" s="2">
-        <v>0</v>
-      </c>
-      <c r="I67" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>0</v>
-      </c>
-      <c r="B68" s="2">
-        <v>0</v>
-      </c>
-      <c r="C68" s="2">
-        <v>0</v>
-      </c>
-      <c r="D68" s="2">
-        <v>0</v>
-      </c>
-      <c r="E68" s="2">
-        <v>0</v>
-      </c>
-      <c r="F68" s="2">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2">
-        <v>0</v>
-      </c>
-      <c r="H68" s="2">
-        <v>0</v>
-      </c>
-      <c r="I68" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
-        <v>191000000000000</v>
-      </c>
-      <c r="B70" s="4">
-        <v>0</v>
-      </c>
-      <c r="C70" s="4">
-        <v>16440</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
-        <v>50800</v>
-      </c>
-      <c r="B71" s="4">
-        <v>2.67</v>
-      </c>
-      <c r="C71" s="4">
-        <v>6292</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
-        <v>216000000</v>
-      </c>
-      <c r="B72" s="4">
-        <v>1.51</v>
-      </c>
-      <c r="C72" s="4">
-        <v>3430</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
-        <v>2970000</v>
-      </c>
-      <c r="B73" s="4">
-        <v>2.02</v>
-      </c>
-      <c r="C73" s="4">
-        <v>13400</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B74" s="4">
-        <v>104400</v>
-      </c>
-      <c r="C74" s="4"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B75" s="4">
-        <v>118900</v>
-      </c>
-      <c r="C75" s="4"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B76" s="4">
-        <v>102100</v>
-      </c>
-      <c r="C76" s="4"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B77" s="4">
-        <v>118500</v>
-      </c>
-      <c r="C77" s="4"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
-        <v>1480000000000</v>
-      </c>
-      <c r="B78" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="C78" s="4">
-        <v>0</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
-        <v>16600000000000</v>
-      </c>
-      <c r="B79" s="4">
-        <v>0</v>
-      </c>
-      <c r="C79" s="4">
-        <v>823</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="3">
-        <v>70800000000000</v>
-      </c>
-      <c r="B80" s="4">
-        <v>0</v>
-      </c>
-      <c r="C80" s="4">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
-        <v>32500000000000</v>
-      </c>
-      <c r="B81" s="4">
-        <v>0</v>
-      </c>
-      <c r="C81" s="4">
-        <v>0</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
-        <v>28900000000000</v>
-      </c>
-      <c r="B82" s="4">
-        <v>0</v>
-      </c>
-      <c r="C82" s="4">
-        <v>-497</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B83" s="4">
-        <v>50670</v>
-      </c>
-      <c r="C83" s="4"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B84" s="4">
-        <v>37060</v>
-      </c>
-      <c r="C84" s="4"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
-        <v>295000000000000</v>
-      </c>
-      <c r="B85" s="4">
-        <v>0</v>
-      </c>
-      <c r="C85" s="4">
-        <v>48430</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
-        <v>24100000000000</v>
-      </c>
-      <c r="B86" s="4">
-        <v>0</v>
-      </c>
-      <c r="C86" s="4">
-        <v>3970</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
-        <v>60300000000000</v>
-      </c>
-      <c r="B87" s="4">
-        <v>0</v>
-      </c>
-      <c r="C87" s="4">
-        <v>7950</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
-        <v>9550000</v>
-      </c>
-      <c r="B88" s="4">
-        <v>2</v>
-      </c>
-      <c r="C88" s="4">
-        <v>3970</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
-        <v>1000000000000</v>
-      </c>
-      <c r="B89" s="4">
-        <v>0</v>
-      </c>
-      <c r="C89" s="4">
-        <v>0</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
-        <v>10700000000000</v>
-      </c>
-      <c r="B90" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="C90" s="4">
-        <v>40450</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <v>0</v>
-      </c>
-      <c r="B93" s="2">
-        <v>0</v>
-      </c>
-      <c r="C93" s="2">
-        <v>0</v>
-      </c>
-      <c r="D93" s="2">
-        <v>0</v>
-      </c>
-      <c r="E93" s="2">
-        <v>0</v>
-      </c>
-      <c r="F93" s="2">
-        <v>0</v>
-      </c>
-      <c r="G93" s="2">
-        <v>0</v>
-      </c>
-      <c r="H93" s="2">
-        <v>0</v>
-      </c>
-      <c r="I93" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>0</v>
-      </c>
-      <c r="B94" s="2">
-        <v>0</v>
-      </c>
-      <c r="C94" s="2">
-        <v>0</v>
-      </c>
-      <c r="D94" s="2">
-        <v>0</v>
-      </c>
-      <c r="E94" s="2">
-        <v>0</v>
-      </c>
-      <c r="F94" s="2">
-        <v>0</v>
-      </c>
-      <c r="G94" s="2">
-        <v>0</v>
-      </c>
-      <c r="H94" s="2">
-        <v>0</v>
-      </c>
-      <c r="I94" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <v>0</v>
-      </c>
-      <c r="B95" s="2">
-        <v>0</v>
-      </c>
-      <c r="C95" s="2">
-        <v>0</v>
-      </c>
-      <c r="D95" s="2">
-        <v>0</v>
-      </c>
-      <c r="E95" s="2">
-        <v>0</v>
-      </c>
-      <c r="F95" s="2">
-        <v>0</v>
-      </c>
-      <c r="G95" s="2">
-        <v>0</v>
-      </c>
-      <c r="H95" s="2">
-        <v>0</v>
-      </c>
-      <c r="I95" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>0</v>
-      </c>
-      <c r="B96" s="2">
-        <v>0</v>
-      </c>
-      <c r="C96" s="2">
-        <v>0</v>
-      </c>
-      <c r="D96" s="2">
-        <v>0</v>
-      </c>
-      <c r="E96" s="2">
-        <v>0</v>
-      </c>
-      <c r="F96" s="2">
-        <v>0</v>
-      </c>
-      <c r="G96" s="2">
-        <v>0</v>
-      </c>
-      <c r="H96" s="2">
-        <v>0</v>
-      </c>
-      <c r="I96" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="B97" s="2">
-        <v>1</v>
-      </c>
-      <c r="C97" s="2">
-        <v>1</v>
-      </c>
-      <c r="D97" s="2">
-        <v>1</v>
-      </c>
-      <c r="E97" s="2">
-        <v>1</v>
-      </c>
-      <c r="F97" s="2">
-        <v>1</v>
-      </c>
-      <c r="G97" s="2">
-        <v>1</v>
-      </c>
-      <c r="H97" s="2">
-        <v>12</v>
-      </c>
-      <c r="I97" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="B98" s="2">
-        <v>1</v>
-      </c>
-      <c r="C98" s="2">
-        <v>1</v>
-      </c>
-      <c r="D98" s="2">
-        <v>1</v>
-      </c>
-      <c r="E98" s="2">
-        <v>1</v>
-      </c>
-      <c r="F98" s="2">
-        <v>1</v>
-      </c>
-      <c r="G98" s="2">
-        <v>1</v>
-      </c>
-      <c r="H98" s="2">
-        <v>12</v>
-      </c>
-      <c r="I98" s="2">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="B99" s="2">
-        <v>1</v>
-      </c>
-      <c r="C99" s="2">
-        <v>1</v>
-      </c>
-      <c r="D99" s="2">
-        <v>1</v>
-      </c>
-      <c r="E99" s="2">
-        <v>1</v>
-      </c>
-      <c r="F99" s="2">
-        <v>1</v>
-      </c>
-      <c r="G99" s="2">
-        <v>1</v>
-      </c>
-      <c r="H99" s="2">
-        <v>12</v>
-      </c>
-      <c r="I99" s="2">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
-        <v>0.73</v>
-      </c>
-      <c r="B100" s="2">
-        <v>1</v>
-      </c>
-      <c r="C100" s="2">
-        <v>1</v>
-      </c>
-      <c r="D100" s="2">
-        <v>1</v>
-      </c>
-      <c r="E100" s="2">
-        <v>1</v>
-      </c>
-      <c r="F100" s="2">
-        <v>1</v>
-      </c>
-      <c r="G100" s="2">
-        <v>1</v>
-      </c>
-      <c r="H100" s="2">
-        <v>12</v>
-      </c>
-      <c r="I100" s="2">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="B101" s="2">
-        <v>1</v>
-      </c>
-      <c r="C101" s="2">
-        <v>1</v>
-      </c>
-      <c r="D101" s="2">
-        <v>1</v>
-      </c>
-      <c r="E101" s="2">
-        <v>1</v>
-      </c>
-      <c r="F101" s="2">
-        <v>1</v>
-      </c>
-      <c r="G101" s="2">
-        <v>1</v>
-      </c>
-      <c r="H101" s="2">
-        <v>14</v>
-      </c>
-      <c r="I101" s="2">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
-        <v>0</v>
-      </c>
-      <c r="B102" s="2">
-        <v>0</v>
-      </c>
-      <c r="C102" s="2">
-        <v>0</v>
-      </c>
-      <c r="D102" s="2">
-        <v>0</v>
-      </c>
-      <c r="E102" s="2">
-        <v>0</v>
-      </c>
-      <c r="F102" s="2">
-        <v>0</v>
-      </c>
-      <c r="G102" s="2">
-        <v>0</v>
-      </c>
-      <c r="H102" s="2">
-        <v>0</v>
-      </c>
-      <c r="I102" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
-        <v>0</v>
-      </c>
-      <c r="B103" s="2">
-        <v>0</v>
-      </c>
-      <c r="C103" s="2">
-        <v>0</v>
-      </c>
-      <c r="D103" s="2">
-        <v>0</v>
-      </c>
-      <c r="E103" s="2">
-        <v>0</v>
-      </c>
-      <c r="F103" s="2">
-        <v>0</v>
-      </c>
-      <c r="G103" s="2">
-        <v>0</v>
-      </c>
-      <c r="H103" s="2">
-        <v>0</v>
-      </c>
-      <c r="I103" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
-        <v>0</v>
-      </c>
-      <c r="B104" s="2">
-        <v>0</v>
-      </c>
-      <c r="C104" s="2">
-        <v>0</v>
-      </c>
-      <c r="D104" s="2">
-        <v>0</v>
-      </c>
-      <c r="E104" s="2">
-        <v>0</v>
-      </c>
-      <c r="F104" s="2">
-        <v>0</v>
-      </c>
-      <c r="G104" s="2">
-        <v>0</v>
-      </c>
-      <c r="H104" s="2">
-        <v>0</v>
-      </c>
-      <c r="I104" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
-        <v>0</v>
-      </c>
-      <c r="B105" s="2">
-        <v>0</v>
-      </c>
-      <c r="C105" s="2">
-        <v>0</v>
-      </c>
-      <c r="D105" s="2">
-        <v>0</v>
-      </c>
-      <c r="E105" s="2">
-        <v>0</v>
-      </c>
-      <c r="F105" s="2">
-        <v>0</v>
-      </c>
-      <c r="G105" s="2">
-        <v>0</v>
-      </c>
-      <c r="H105" s="2">
-        <v>0</v>
-      </c>
-      <c r="I105" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
-        <v>0</v>
-      </c>
-      <c r="B106" s="2">
-        <v>0</v>
-      </c>
-      <c r="C106" s="2">
-        <v>0</v>
-      </c>
-      <c r="D106" s="2">
-        <v>0</v>
-      </c>
-      <c r="E106" s="2">
-        <v>0</v>
-      </c>
-      <c r="F106" s="2">
-        <v>0</v>
-      </c>
-      <c r="G106" s="2">
-        <v>0</v>
-      </c>
-      <c r="H106" s="2">
-        <v>0</v>
-      </c>
-      <c r="I106" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
-        <v>0</v>
-      </c>
-      <c r="B107" s="2">
-        <v>0</v>
-      </c>
-      <c r="C107" s="2">
-        <v>0</v>
-      </c>
-      <c r="D107" s="2">
-        <v>0</v>
-      </c>
-      <c r="E107" s="2">
-        <v>0</v>
-      </c>
-      <c r="F107" s="2">
-        <v>0</v>
-      </c>
-      <c r="G107" s="2">
-        <v>0</v>
-      </c>
-      <c r="H107" s="2">
-        <v>0</v>
-      </c>
-      <c r="I107" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="B108" s="2">
-        <v>1</v>
-      </c>
-      <c r="C108" s="2">
-        <v>1</v>
-      </c>
-      <c r="D108" s="2">
-        <v>1</v>
-      </c>
-      <c r="E108" s="2">
-        <v>1</v>
-      </c>
-      <c r="F108" s="2">
-        <v>1</v>
-      </c>
-      <c r="G108" s="2">
-        <v>1</v>
-      </c>
-      <c r="H108" s="2">
-        <v>12</v>
-      </c>
-      <c r="I108" s="2">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
-        <v>0</v>
-      </c>
-      <c r="B109" s="2">
-        <v>0</v>
-      </c>
-      <c r="C109" s="2">
-        <v>0</v>
-      </c>
-      <c r="D109" s="2">
-        <v>0</v>
-      </c>
-      <c r="E109" s="2">
-        <v>0</v>
-      </c>
-      <c r="F109" s="2">
-        <v>0</v>
-      </c>
-      <c r="G109" s="2">
-        <v>0</v>
-      </c>
-      <c r="H109" s="2">
-        <v>0</v>
-      </c>
-      <c r="I109" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
-        <v>0</v>
-      </c>
-      <c r="B110" s="2">
-        <v>0</v>
-      </c>
-      <c r="C110" s="2">
-        <v>0</v>
-      </c>
-      <c r="D110" s="2">
-        <v>0</v>
-      </c>
-      <c r="E110" s="2">
-        <v>0</v>
-      </c>
-      <c r="F110" s="2">
-        <v>0</v>
-      </c>
-      <c r="G110" s="2">
-        <v>0</v>
-      </c>
-      <c r="H110" s="2">
-        <v>0</v>
-      </c>
-      <c r="I110" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
-        <v>0</v>
-      </c>
-      <c r="B111" s="2">
-        <v>0</v>
-      </c>
-      <c r="C111" s="2">
-        <v>0</v>
-      </c>
-      <c r="D111" s="2">
-        <v>0</v>
-      </c>
-      <c r="E111" s="2">
-        <v>0</v>
-      </c>
-      <c r="F111" s="2">
-        <v>0</v>
-      </c>
-      <c r="G111" s="2">
-        <v>0</v>
-      </c>
-      <c r="H111" s="2">
-        <v>0</v>
-      </c>
-      <c r="I111" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
-        <v>0</v>
-      </c>
-      <c r="B112" s="2">
-        <v>0</v>
-      </c>
-      <c r="C112" s="2">
-        <v>0</v>
-      </c>
-      <c r="D112" s="2">
-        <v>0</v>
-      </c>
-      <c r="E112" s="2">
-        <v>0</v>
-      </c>
-      <c r="F112" s="2">
-        <v>0</v>
-      </c>
-      <c r="G112" s="2">
-        <v>0</v>
-      </c>
-      <c r="H112" s="2">
-        <v>0</v>
-      </c>
-      <c r="I112" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
-        <v>0</v>
-      </c>
-      <c r="B113" s="2">
-        <v>0</v>
-      </c>
-      <c r="C113" s="2">
-        <v>0</v>
-      </c>
-      <c r="D113" s="2">
-        <v>0</v>
-      </c>
-      <c r="E113" s="2">
-        <v>0</v>
-      </c>
-      <c r="F113" s="2">
-        <v>0</v>
-      </c>
-      <c r="G113" s="2">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2">
-        <v>0</v>
-      </c>
-      <c r="I113" s="2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11030,6 +8425,1202 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF854AEA-9F86-4B97-9820-34FDF5731FEA}">
+  <dimension ref="A1:U65"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" style="20"/>
+    <col min="21" max="21" width="12.5546875" style="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>0</v>
+      </c>
+      <c r="B6" s="9">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>0</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>0</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>0</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>0</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>0</v>
+      </c>
+      <c r="B11" s="9">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>1</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>0</v>
+      </c>
+      <c r="B14" s="9">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>2</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>0</v>
+      </c>
+      <c r="B15" s="9">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9">
+        <v>2</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
+        <v>0</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>0</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>0</v>
+      </c>
+      <c r="B18" s="9">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>2</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>1</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>0</v>
+      </c>
+      <c r="I19" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>0</v>
+      </c>
+      <c r="B20" s="9">
+        <v>0</v>
+      </c>
+      <c r="C20" s="9">
+        <v>1</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>1</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>0</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>1</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>1</v>
+      </c>
+      <c r="B23" s="9">
+        <v>1</v>
+      </c>
+      <c r="C23" s="9">
+        <v>1</v>
+      </c>
+      <c r="D23" s="9">
+        <v>1</v>
+      </c>
+      <c r="E23" s="9">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1</v>
+      </c>
+      <c r="G23" s="9">
+        <v>1</v>
+      </c>
+      <c r="H23" s="9">
+        <v>1</v>
+      </c>
+      <c r="I23" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
+        <v>1</v>
+      </c>
+      <c r="B24" s="9">
+        <v>1</v>
+      </c>
+      <c r="C24" s="9">
+        <v>1</v>
+      </c>
+      <c r="D24" s="9">
+        <v>1</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1</v>
+      </c>
+      <c r="F24" s="9">
+        <v>1</v>
+      </c>
+      <c r="G24" s="9">
+        <v>1</v>
+      </c>
+      <c r="H24" s="9">
+        <v>1</v>
+      </c>
+      <c r="I24" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>1</v>
+      </c>
+      <c r="B25" s="9">
+        <v>1</v>
+      </c>
+      <c r="C25" s="9">
+        <v>1</v>
+      </c>
+      <c r="D25" s="9">
+        <v>1</v>
+      </c>
+      <c r="E25" s="9">
+        <v>1</v>
+      </c>
+      <c r="F25" s="9">
+        <v>1</v>
+      </c>
+      <c r="G25" s="9">
+        <v>1</v>
+      </c>
+      <c r="H25" s="9">
+        <v>1</v>
+      </c>
+      <c r="I25" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>1</v>
+      </c>
+      <c r="B26" s="9">
+        <v>1</v>
+      </c>
+      <c r="C26" s="9">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9">
+        <v>1</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1</v>
+      </c>
+      <c r="F26" s="9">
+        <v>1</v>
+      </c>
+      <c r="G26" s="9">
+        <v>1</v>
+      </c>
+      <c r="H26" s="9">
+        <v>1</v>
+      </c>
+      <c r="I26" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>0</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>0</v>
+      </c>
+      <c r="B28" s="9">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
+      <c r="I28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>0</v>
+      </c>
+      <c r="B29" s="9">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>0</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>0</v>
+      </c>
+      <c r="B30" s="9">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="23"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <v>5.5E+18</v>
+      </c>
+      <c r="B32" s="19">
+        <v>-1</v>
+      </c>
+      <c r="C32" s="23">
+        <v>103300</v>
+      </c>
+      <c r="D32" s="14">
+        <v>1800000000000000</v>
+      </c>
+      <c r="E32" s="19">
+        <v>-1</v>
+      </c>
+      <c r="F32" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <v>7.2E+18</v>
+      </c>
+      <c r="B33" s="19">
+        <v>-1</v>
+      </c>
+      <c r="C33" s="23">
+        <v>117910</v>
+      </c>
+      <c r="D33" s="14">
+        <v>400000000000000</v>
+      </c>
+      <c r="E33" s="19">
+        <v>-1</v>
+      </c>
+      <c r="F33" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <v>5.2E+21</v>
+      </c>
+      <c r="B34" s="19">
+        <v>-1.5</v>
+      </c>
+      <c r="C34" s="23">
+        <v>118000</v>
+      </c>
+      <c r="D34" s="14">
+        <v>4.4E+17</v>
+      </c>
+      <c r="E34" s="19">
+        <v>-1.5</v>
+      </c>
+      <c r="F34" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <v>8.5E+18</v>
+      </c>
+      <c r="B35" s="19">
+        <v>-1</v>
+      </c>
+      <c r="C35" s="23">
+        <v>101000</v>
+      </c>
+      <c r="D35" s="14">
+        <v>7100000000000000</v>
+      </c>
+      <c r="E35" s="19">
+        <v>-1</v>
+      </c>
+      <c r="F35" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <v>58000000000000</v>
+      </c>
+      <c r="B36" s="19">
+        <v>0</v>
+      </c>
+      <c r="C36" s="23">
+        <v>18000</v>
+      </c>
+      <c r="D36" s="14">
+        <v>5300000000000</v>
+      </c>
+      <c r="E36" s="19">
+        <v>0</v>
+      </c>
+      <c r="F36" s="23">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <v>84000000000000</v>
+      </c>
+      <c r="B37" s="19">
+        <v>0</v>
+      </c>
+      <c r="C37" s="23">
+        <v>20100</v>
+      </c>
+      <c r="D37" s="14">
+        <v>20000000000000</v>
+      </c>
+      <c r="E37" s="19">
+        <v>0</v>
+      </c>
+      <c r="F37" s="23">
+        <v>5166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <v>220000000000000</v>
+      </c>
+      <c r="B38" s="19">
+        <v>0</v>
+      </c>
+      <c r="C38" s="23">
+        <v>16800</v>
+      </c>
+      <c r="D38" s="14">
+        <v>15000000000000</v>
+      </c>
+      <c r="E38" s="19">
+        <v>0</v>
+      </c>
+      <c r="F38" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <v>75000000000000</v>
+      </c>
+      <c r="B39" s="19">
+        <v>0</v>
+      </c>
+      <c r="C39" s="23">
+        <v>11100</v>
+      </c>
+      <c r="D39" s="14">
+        <v>30000000000000</v>
+      </c>
+      <c r="E39" s="19">
+        <v>0</v>
+      </c>
+      <c r="F39" s="23">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+    </row>
+    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+    </row>
+    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+    </row>
+    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D62" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+    </row>
+    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CD23AF9-4AAA-476C-A75B-6CE20E16E2E9}">
   <dimension ref="A1:V84"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -12946,7 +11537,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="12">
-        <v>100000000000</v>
+        <v>100000000000000</v>
       </c>
       <c r="B65" s="13">
         <v>0</v>
@@ -12960,7 +11551,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="12">
-        <v>260000000000</v>
+        <v>260000000000000</v>
       </c>
       <c r="B66" s="13">
         <v>0</v>
@@ -12974,7 +11565,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="12">
-        <v>18000000</v>
+        <v>18000000000</v>
       </c>
       <c r="B67" s="13">
         <v>1</v>
@@ -12985,7 +11576,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="12">
-        <v>22000000000</v>
+        <v>22000000000000</v>
       </c>
       <c r="B68" s="13">
         <v>0</v>
@@ -12996,7 +11587,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
-        <v>6300000000</v>
+        <v>6300000000000</v>
       </c>
       <c r="B69" s="9">
         <v>0</v>
@@ -13007,7 +11598,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
-        <v>2.2E+16</v>
+        <v>2.2E+19</v>
       </c>
       <c r="B70" s="9">
         <v>-2</v>
@@ -13018,7 +11609,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
-        <v>640000000000</v>
+        <v>640000000000000</v>
       </c>
       <c r="B71" s="9">
         <v>-1</v>
@@ -13029,7 +11620,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="12">
-        <v>60000000000</v>
+        <v>60000000000000</v>
       </c>
       <c r="B72" s="9">
         <v>-0.6</v>
@@ -13043,7 +11634,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
-        <v>2100000000</v>
+        <v>2100000000000</v>
       </c>
       <c r="B73" s="13">
         <v>0</v>
@@ -13057,7 +11648,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
-        <v>140000000000</v>
+        <v>140000000000000</v>
       </c>
       <c r="B74" s="13">
         <v>0</v>
@@ -13068,7 +11659,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="12">
-        <v>10000000000</v>
+        <v>10000000000000</v>
       </c>
       <c r="B75" s="13">
         <v>0</v>
@@ -13082,7 +11673,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="12">
-        <v>15000000000</v>
+        <v>15000000000000</v>
       </c>
       <c r="B76" s="13">
         <v>0</v>
@@ -13096,7 +11687,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="12">
-        <v>8000000000</v>
+        <v>8000000000000</v>
       </c>
       <c r="B77" s="9">
         <v>0</v>
@@ -13107,7 +11698,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="12">
-        <v>2000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="B78" s="9">
         <v>0</v>
@@ -13118,7 +11709,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="12">
-        <v>1400000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="B79" s="13">
         <v>0</v>
@@ -13129,7 +11720,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="12">
-        <v>14000000000</v>
+        <v>14000000000000</v>
       </c>
       <c r="B80" s="13">
         <v>0</v>
@@ -13143,7 +11734,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="12">
-        <v>6100000000</v>
+        <v>6100000000000</v>
       </c>
       <c r="B81" s="13">
         <v>0</v>
@@ -13157,7 +11748,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="12">
-        <v>120000000000000</v>
+        <v>1.2E+17</v>
       </c>
       <c r="B82" s="13">
         <v>0</v>
@@ -13168,7 +11759,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="12">
-        <v>60000000</v>
+        <v>60000000000</v>
       </c>
       <c r="B83" s="13">
         <v>0</v>
@@ -13183,6 +11774,5532 @@
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D84" s="2" t="s">
         <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I113"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <v>2</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <v>2</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>1</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2">
+        <v>1</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2">
+        <v>0</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2">
+        <v>1</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0</v>
+      </c>
+      <c r="C48" s="2">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0</v>
+      </c>
+      <c r="C50" s="2">
+        <v>0</v>
+      </c>
+      <c r="D50" s="2">
+        <v>0</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0</v>
+      </c>
+      <c r="D51" s="2">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B52" s="2">
+        <v>1</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2">
+        <v>1</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2">
+        <v>12</v>
+      </c>
+      <c r="I52" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B53" s="2">
+        <v>1</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2">
+        <v>1</v>
+      </c>
+      <c r="F53" s="2">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2">
+        <v>12</v>
+      </c>
+      <c r="I53" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B54" s="2">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2">
+        <v>1</v>
+      </c>
+      <c r="E54" s="2">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1</v>
+      </c>
+      <c r="H54" s="2">
+        <v>12</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="B55" s="2">
+        <v>1</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2">
+        <v>1</v>
+      </c>
+      <c r="F55" s="2">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2">
+        <v>1</v>
+      </c>
+      <c r="H55" s="2">
+        <v>12</v>
+      </c>
+      <c r="I55" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="B56" s="2">
+        <v>1</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2">
+        <v>1</v>
+      </c>
+      <c r="H56" s="2">
+        <v>14</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>0</v>
+      </c>
+      <c r="B57" s="2">
+        <v>0</v>
+      </c>
+      <c r="C57" s="2">
+        <v>0</v>
+      </c>
+      <c r="D57" s="2">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0</v>
+      </c>
+      <c r="G57" s="2">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2">
+        <v>0</v>
+      </c>
+      <c r="C58" s="2">
+        <v>0</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>0</v>
+      </c>
+      <c r="B59" s="2">
+        <v>0</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2">
+        <v>0</v>
+      </c>
+      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0</v>
+      </c>
+      <c r="C60" s="2">
+        <v>0</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>0</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0</v>
+      </c>
+      <c r="C61" s="2">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="2">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2">
+        <v>0</v>
+      </c>
+      <c r="C62" s="2">
+        <v>0</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0</v>
+      </c>
+      <c r="E62" s="2">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2">
+        <v>0</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B63" s="2">
+        <v>1</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2">
+        <v>1</v>
+      </c>
+      <c r="E63" s="2">
+        <v>1</v>
+      </c>
+      <c r="F63" s="2">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2">
+        <v>1</v>
+      </c>
+      <c r="H63" s="2">
+        <v>12</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>0</v>
+      </c>
+      <c r="B64" s="2">
+        <v>0</v>
+      </c>
+      <c r="C64" s="2">
+        <v>0</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>0</v>
+      </c>
+      <c r="B65" s="2">
+        <v>0</v>
+      </c>
+      <c r="C65" s="2">
+        <v>0</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2">
+        <v>0</v>
+      </c>
+      <c r="I65" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>0</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0</v>
+      </c>
+      <c r="C66" s="2">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0</v>
+      </c>
+      <c r="C67" s="2">
+        <v>0</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2">
+        <v>0</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0</v>
+      </c>
+      <c r="C68" s="2">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>191000000000000</v>
+      </c>
+      <c r="B70" s="4">
+        <v>0</v>
+      </c>
+      <c r="C70" s="4">
+        <v>16440</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <v>50800</v>
+      </c>
+      <c r="B71" s="4">
+        <v>2.67</v>
+      </c>
+      <c r="C71" s="4">
+        <v>6292</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <v>216000000</v>
+      </c>
+      <c r="B72" s="4">
+        <v>1.51</v>
+      </c>
+      <c r="C72" s="4">
+        <v>3430</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
+        <v>2970000</v>
+      </c>
+      <c r="B73" s="4">
+        <v>2.02</v>
+      </c>
+      <c r="C73" s="4">
+        <v>13400</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B74" s="4">
+        <v>104400</v>
+      </c>
+      <c r="C74" s="4"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B75" s="4">
+        <v>118900</v>
+      </c>
+      <c r="C75" s="4"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B76" s="4">
+        <v>102100</v>
+      </c>
+      <c r="C76" s="4"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B77" s="4">
+        <v>118500</v>
+      </c>
+      <c r="C77" s="4"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>1480000000000</v>
+      </c>
+      <c r="B78" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C78" s="4">
+        <v>0</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>16600000000000</v>
+      </c>
+      <c r="B79" s="4">
+        <v>0</v>
+      </c>
+      <c r="C79" s="4">
+        <v>823</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>70800000000000</v>
+      </c>
+      <c r="B80" s="4">
+        <v>0</v>
+      </c>
+      <c r="C80" s="4">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>32500000000000</v>
+      </c>
+      <c r="B81" s="4">
+        <v>0</v>
+      </c>
+      <c r="C81" s="4">
+        <v>0</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>28900000000000</v>
+      </c>
+      <c r="B82" s="4">
+        <v>0</v>
+      </c>
+      <c r="C82" s="4">
+        <v>-497</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" s="4">
+        <v>50670</v>
+      </c>
+      <c r="C83" s="4"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B84" s="4">
+        <v>37060</v>
+      </c>
+      <c r="C84" s="4"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
+        <v>295000000000000</v>
+      </c>
+      <c r="B85" s="4">
+        <v>0</v>
+      </c>
+      <c r="C85" s="4">
+        <v>48430</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
+        <v>24100000000000</v>
+      </c>
+      <c r="B86" s="4">
+        <v>0</v>
+      </c>
+      <c r="C86" s="4">
+        <v>3970</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <v>60300000000000</v>
+      </c>
+      <c r="B87" s="4">
+        <v>0</v>
+      </c>
+      <c r="C87" s="4">
+        <v>7950</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
+        <v>9550000</v>
+      </c>
+      <c r="B88" s="4">
+        <v>2</v>
+      </c>
+      <c r="C88" s="4">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <v>1000000000000</v>
+      </c>
+      <c r="B89" s="4">
+        <v>0</v>
+      </c>
+      <c r="C89" s="4">
+        <v>0</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>10700000000000</v>
+      </c>
+      <c r="B90" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C90" s="4">
+        <v>40450</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>0</v>
+      </c>
+      <c r="B93" s="2">
+        <v>0</v>
+      </c>
+      <c r="C93" s="2">
+        <v>0</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>0</v>
+      </c>
+      <c r="B94" s="2">
+        <v>0</v>
+      </c>
+      <c r="C94" s="2">
+        <v>0</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>0</v>
+      </c>
+      <c r="B95" s="2">
+        <v>0</v>
+      </c>
+      <c r="C95" s="2">
+        <v>0</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2">
+        <v>0</v>
+      </c>
+      <c r="I95" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>0</v>
+      </c>
+      <c r="B96" s="2">
+        <v>0</v>
+      </c>
+      <c r="C96" s="2">
+        <v>0</v>
+      </c>
+      <c r="D96" s="2">
+        <v>0</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B97" s="2">
+        <v>1</v>
+      </c>
+      <c r="C97" s="2">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2">
+        <v>1</v>
+      </c>
+      <c r="E97" s="2">
+        <v>1</v>
+      </c>
+      <c r="F97" s="2">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2">
+        <v>1</v>
+      </c>
+      <c r="H97" s="2">
+        <v>12</v>
+      </c>
+      <c r="I97" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B98" s="2">
+        <v>1</v>
+      </c>
+      <c r="C98" s="2">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2">
+        <v>1</v>
+      </c>
+      <c r="E98" s="2">
+        <v>1</v>
+      </c>
+      <c r="F98" s="2">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2">
+        <v>1</v>
+      </c>
+      <c r="H98" s="2">
+        <v>12</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B99" s="2">
+        <v>1</v>
+      </c>
+      <c r="C99" s="2">
+        <v>1</v>
+      </c>
+      <c r="D99" s="2">
+        <v>1</v>
+      </c>
+      <c r="E99" s="2">
+        <v>1</v>
+      </c>
+      <c r="F99" s="2">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2">
+        <v>1</v>
+      </c>
+      <c r="H99" s="2">
+        <v>12</v>
+      </c>
+      <c r="I99" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="B100" s="2">
+        <v>1</v>
+      </c>
+      <c r="C100" s="2">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2">
+        <v>1</v>
+      </c>
+      <c r="E100" s="2">
+        <v>1</v>
+      </c>
+      <c r="F100" s="2">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2">
+        <v>1</v>
+      </c>
+      <c r="H100" s="2">
+        <v>12</v>
+      </c>
+      <c r="I100" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="B101" s="2">
+        <v>1</v>
+      </c>
+      <c r="C101" s="2">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2">
+        <v>1</v>
+      </c>
+      <c r="E101" s="2">
+        <v>1</v>
+      </c>
+      <c r="F101" s="2">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2">
+        <v>1</v>
+      </c>
+      <c r="H101" s="2">
+        <v>14</v>
+      </c>
+      <c r="I101" s="2">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>0</v>
+      </c>
+      <c r="B102" s="2">
+        <v>0</v>
+      </c>
+      <c r="C102" s="2">
+        <v>0</v>
+      </c>
+      <c r="D102" s="2">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2">
+        <v>0</v>
+      </c>
+      <c r="G102" s="2">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2">
+        <v>0</v>
+      </c>
+      <c r="C103" s="2">
+        <v>0</v>
+      </c>
+      <c r="D103" s="2">
+        <v>0</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2">
+        <v>0</v>
+      </c>
+      <c r="G103" s="2">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2">
+        <v>0</v>
+      </c>
+      <c r="I103" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>0</v>
+      </c>
+      <c r="B104" s="2">
+        <v>0</v>
+      </c>
+      <c r="C104" s="2">
+        <v>0</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2">
+        <v>0</v>
+      </c>
+      <c r="G104" s="2">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2">
+        <v>0</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>0</v>
+      </c>
+      <c r="B105" s="2">
+        <v>0</v>
+      </c>
+      <c r="C105" s="2">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2">
+        <v>0</v>
+      </c>
+      <c r="G105" s="2">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2">
+        <v>0</v>
+      </c>
+      <c r="I105" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>0</v>
+      </c>
+      <c r="B106" s="2">
+        <v>0</v>
+      </c>
+      <c r="C106" s="2">
+        <v>0</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2">
+        <v>0</v>
+      </c>
+      <c r="G106" s="2">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2">
+        <v>0</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>0</v>
+      </c>
+      <c r="B107" s="2">
+        <v>0</v>
+      </c>
+      <c r="C107" s="2">
+        <v>0</v>
+      </c>
+      <c r="D107" s="2">
+        <v>0</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2">
+        <v>0</v>
+      </c>
+      <c r="G107" s="2">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2">
+        <v>0</v>
+      </c>
+      <c r="I107" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B108" s="2">
+        <v>1</v>
+      </c>
+      <c r="C108" s="2">
+        <v>1</v>
+      </c>
+      <c r="D108" s="2">
+        <v>1</v>
+      </c>
+      <c r="E108" s="2">
+        <v>1</v>
+      </c>
+      <c r="F108" s="2">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2">
+        <v>1</v>
+      </c>
+      <c r="H108" s="2">
+        <v>12</v>
+      </c>
+      <c r="I108" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>0</v>
+      </c>
+      <c r="B109" s="2">
+        <v>0</v>
+      </c>
+      <c r="C109" s="2">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+      <c r="E109" s="2">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2">
+        <v>0</v>
+      </c>
+      <c r="G109" s="2">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2">
+        <v>0</v>
+      </c>
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>0</v>
+      </c>
+      <c r="B110" s="2">
+        <v>0</v>
+      </c>
+      <c r="C110" s="2">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2">
+        <v>0</v>
+      </c>
+      <c r="G110" s="2">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2">
+        <v>0</v>
+      </c>
+      <c r="I110" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>0</v>
+      </c>
+      <c r="B111" s="2">
+        <v>0</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2">
+        <v>0</v>
+      </c>
+      <c r="E111" s="2">
+        <v>0</v>
+      </c>
+      <c r="F111" s="2">
+        <v>0</v>
+      </c>
+      <c r="G111" s="2">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2">
+        <v>0</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>0</v>
+      </c>
+      <c r="B112" s="2">
+        <v>0</v>
+      </c>
+      <c r="C112" s="2">
+        <v>0</v>
+      </c>
+      <c r="D112" s="2">
+        <v>0</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0</v>
+      </c>
+      <c r="F112" s="2">
+        <v>0</v>
+      </c>
+      <c r="G112" s="2">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2">
+        <v>0</v>
+      </c>
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>0</v>
+      </c>
+      <c r="B113" s="2">
+        <v>0</v>
+      </c>
+      <c r="C113" s="2">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2">
+        <v>0</v>
+      </c>
+      <c r="E113" s="2">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2">
+        <v>0</v>
+      </c>
+      <c r="G113" s="2">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2">
+        <v>0</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8B9947A-9540-4CB8-88B6-7B4D0332E7C6}">
+  <dimension ref="A1:R107"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="9" width="10.77734375" style="18" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="16" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="17"/>
+    <col min="12" max="12" width="11.44140625" style="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
+        <v>2</v>
+      </c>
+      <c r="B2" s="18">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18">
+        <v>0</v>
+      </c>
+      <c r="D2" s="18">
+        <v>0</v>
+      </c>
+      <c r="E2" s="18">
+        <v>0</v>
+      </c>
+      <c r="F2" s="18">
+        <v>0</v>
+      </c>
+      <c r="G2" s="18">
+        <v>0</v>
+      </c>
+      <c r="H2" s="18">
+        <v>0</v>
+      </c>
+      <c r="I2" s="18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18">
+        <v>1</v>
+      </c>
+      <c r="C3" s="18">
+        <v>0</v>
+      </c>
+      <c r="D3" s="18">
+        <v>0</v>
+      </c>
+      <c r="E3" s="18">
+        <v>0</v>
+      </c>
+      <c r="F3" s="18">
+        <v>0</v>
+      </c>
+      <c r="G3" s="18">
+        <v>0</v>
+      </c>
+      <c r="H3" s="18">
+        <v>0</v>
+      </c>
+      <c r="I3" s="18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
+        <v>0</v>
+      </c>
+      <c r="B5" s="19">
+        <v>1</v>
+      </c>
+      <c r="C5" s="19">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19">
+        <v>1</v>
+      </c>
+      <c r="E5" s="19">
+        <v>0</v>
+      </c>
+      <c r="F5" s="19">
+        <v>0</v>
+      </c>
+      <c r="G5" s="19">
+        <v>0</v>
+      </c>
+      <c r="H5" s="19">
+        <v>0</v>
+      </c>
+      <c r="I5" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>1</v>
+      </c>
+      <c r="B6" s="19">
+        <v>0</v>
+      </c>
+      <c r="C6" s="19">
+        <v>1</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0</v>
+      </c>
+      <c r="E6" s="19">
+        <v>0</v>
+      </c>
+      <c r="F6" s="19">
+        <v>0</v>
+      </c>
+      <c r="G6" s="19">
+        <v>0</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
+        <v>1</v>
+      </c>
+      <c r="B7" s="19">
+        <v>0</v>
+      </c>
+      <c r="C7" s="19">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19">
+        <v>0</v>
+      </c>
+      <c r="E7" s="19">
+        <v>1</v>
+      </c>
+      <c r="F7" s="19">
+        <v>0</v>
+      </c>
+      <c r="G7" s="19">
+        <v>0</v>
+      </c>
+      <c r="H7" s="19">
+        <v>0</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
+        <v>0</v>
+      </c>
+      <c r="B8" s="19">
+        <v>0</v>
+      </c>
+      <c r="C8" s="19">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19">
+        <v>0</v>
+      </c>
+      <c r="E8" s="19">
+        <v>2</v>
+      </c>
+      <c r="F8" s="19">
+        <v>0</v>
+      </c>
+      <c r="G8" s="19">
+        <v>0</v>
+      </c>
+      <c r="H8" s="19">
+        <v>0</v>
+      </c>
+      <c r="I8" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
+        <v>0</v>
+      </c>
+      <c r="B9" s="19">
+        <v>0</v>
+      </c>
+      <c r="C9" s="19">
+        <v>2</v>
+      </c>
+      <c r="D9" s="19">
+        <v>0</v>
+      </c>
+      <c r="E9" s="19">
+        <v>0</v>
+      </c>
+      <c r="F9" s="19">
+        <v>0</v>
+      </c>
+      <c r="G9" s="19">
+        <v>0</v>
+      </c>
+      <c r="H9" s="19">
+        <v>0</v>
+      </c>
+      <c r="I9" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>0</v>
+      </c>
+      <c r="B10" s="19">
+        <v>0</v>
+      </c>
+      <c r="C10" s="19">
+        <v>0</v>
+      </c>
+      <c r="D10" s="19">
+        <v>2</v>
+      </c>
+      <c r="E10" s="19">
+        <v>0</v>
+      </c>
+      <c r="F10" s="19">
+        <v>0</v>
+      </c>
+      <c r="G10" s="19">
+        <v>0</v>
+      </c>
+      <c r="H10" s="19">
+        <v>0</v>
+      </c>
+      <c r="I10" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
+        <v>1</v>
+      </c>
+      <c r="B11" s="19">
+        <v>0</v>
+      </c>
+      <c r="C11" s="19">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19">
+        <v>2</v>
+      </c>
+      <c r="E11" s="19">
+        <v>0</v>
+      </c>
+      <c r="F11" s="19">
+        <v>0</v>
+      </c>
+      <c r="G11" s="19">
+        <v>0</v>
+      </c>
+      <c r="H11" s="19">
+        <v>0</v>
+      </c>
+      <c r="I11" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>0</v>
+      </c>
+      <c r="B12" s="19">
+        <v>0</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19">
+        <v>2</v>
+      </c>
+      <c r="E12" s="19">
+        <v>0</v>
+      </c>
+      <c r="F12" s="19">
+        <v>0</v>
+      </c>
+      <c r="G12" s="19">
+        <v>0</v>
+      </c>
+      <c r="H12" s="19">
+        <v>1</v>
+      </c>
+      <c r="I12" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>0</v>
+      </c>
+      <c r="B13" s="19">
+        <v>0</v>
+      </c>
+      <c r="C13" s="19">
+        <v>0</v>
+      </c>
+      <c r="D13" s="19">
+        <v>1</v>
+      </c>
+      <c r="E13" s="19">
+        <v>1</v>
+      </c>
+      <c r="F13" s="19">
+        <v>0</v>
+      </c>
+      <c r="G13" s="19">
+        <v>0</v>
+      </c>
+      <c r="H13" s="19">
+        <v>0</v>
+      </c>
+      <c r="I13" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>0</v>
+      </c>
+      <c r="B14" s="19">
+        <v>1</v>
+      </c>
+      <c r="C14" s="19">
+        <v>0</v>
+      </c>
+      <c r="D14" s="19">
+        <v>1</v>
+      </c>
+      <c r="E14" s="19">
+        <v>0</v>
+      </c>
+      <c r="F14" s="19">
+        <v>0</v>
+      </c>
+      <c r="G14" s="19">
+        <v>0</v>
+      </c>
+      <c r="H14" s="19">
+        <v>0</v>
+      </c>
+      <c r="I14" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>1</v>
+      </c>
+      <c r="B15" s="19">
+        <v>1</v>
+      </c>
+      <c r="C15" s="19">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19">
+        <v>1</v>
+      </c>
+      <c r="E15" s="19">
+        <v>0</v>
+      </c>
+      <c r="F15" s="19">
+        <v>0</v>
+      </c>
+      <c r="G15" s="19">
+        <v>0</v>
+      </c>
+      <c r="H15" s="19">
+        <v>0</v>
+      </c>
+      <c r="I15" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>0</v>
+      </c>
+      <c r="B16" s="19">
+        <v>2</v>
+      </c>
+      <c r="C16" s="19">
+        <v>0</v>
+      </c>
+      <c r="D16" s="19">
+        <v>1</v>
+      </c>
+      <c r="E16" s="19">
+        <v>0</v>
+      </c>
+      <c r="F16" s="19">
+        <v>0</v>
+      </c>
+      <c r="G16" s="19">
+        <v>0</v>
+      </c>
+      <c r="H16" s="19">
+        <v>0</v>
+      </c>
+      <c r="I16" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
+        <v>0</v>
+      </c>
+      <c r="B17" s="19">
+        <v>1</v>
+      </c>
+      <c r="C17" s="19">
+        <v>0</v>
+      </c>
+      <c r="D17" s="19">
+        <v>1</v>
+      </c>
+      <c r="E17" s="19">
+        <v>0</v>
+      </c>
+      <c r="F17" s="19">
+        <v>0</v>
+      </c>
+      <c r="G17" s="19">
+        <v>0</v>
+      </c>
+      <c r="H17" s="19">
+        <v>0</v>
+      </c>
+      <c r="I17" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
+        <v>0</v>
+      </c>
+      <c r="B18" s="19">
+        <v>1</v>
+      </c>
+      <c r="C18" s="19">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19">
+        <v>1</v>
+      </c>
+      <c r="E18" s="19">
+        <v>0</v>
+      </c>
+      <c r="F18" s="19">
+        <v>0</v>
+      </c>
+      <c r="G18" s="19">
+        <v>0</v>
+      </c>
+      <c r="H18" s="19">
+        <v>1</v>
+      </c>
+      <c r="I18" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
+        <v>0</v>
+      </c>
+      <c r="B19" s="19">
+        <v>0</v>
+      </c>
+      <c r="C19" s="19">
+        <v>0</v>
+      </c>
+      <c r="D19" s="19">
+        <v>1</v>
+      </c>
+      <c r="E19" s="19">
+        <v>0</v>
+      </c>
+      <c r="F19" s="19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19">
+        <v>0</v>
+      </c>
+      <c r="I19" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>0</v>
+      </c>
+      <c r="B20" s="19">
+        <v>0</v>
+      </c>
+      <c r="C20" s="19">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19">
+        <v>1</v>
+      </c>
+      <c r="E20" s="19">
+        <v>0</v>
+      </c>
+      <c r="F20" s="19">
+        <v>1</v>
+      </c>
+      <c r="G20" s="19">
+        <v>0</v>
+      </c>
+      <c r="H20" s="19">
+        <v>0</v>
+      </c>
+      <c r="I20" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>0</v>
+      </c>
+      <c r="B21" s="19">
+        <v>0</v>
+      </c>
+      <c r="C21" s="19">
+        <v>0</v>
+      </c>
+      <c r="D21" s="19">
+        <v>1</v>
+      </c>
+      <c r="E21" s="19">
+        <v>0</v>
+      </c>
+      <c r="F21" s="19">
+        <v>1</v>
+      </c>
+      <c r="G21" s="19">
+        <v>0</v>
+      </c>
+      <c r="H21" s="19">
+        <v>0</v>
+      </c>
+      <c r="I21" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
+        <v>0</v>
+      </c>
+      <c r="B22" s="19">
+        <v>0</v>
+      </c>
+      <c r="C22" s="19">
+        <v>1</v>
+      </c>
+      <c r="D22" s="19">
+        <v>0</v>
+      </c>
+      <c r="E22" s="19">
+        <v>0</v>
+      </c>
+      <c r="F22" s="19">
+        <v>1</v>
+      </c>
+      <c r="G22" s="19">
+        <v>0</v>
+      </c>
+      <c r="H22" s="19">
+        <v>0</v>
+      </c>
+      <c r="I22" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
+        <v>0</v>
+      </c>
+      <c r="B23" s="19">
+        <v>0</v>
+      </c>
+      <c r="C23" s="19">
+        <v>0</v>
+      </c>
+      <c r="D23" s="19">
+        <v>0</v>
+      </c>
+      <c r="E23" s="19">
+        <v>1</v>
+      </c>
+      <c r="F23" s="19">
+        <v>1</v>
+      </c>
+      <c r="G23" s="19">
+        <v>0</v>
+      </c>
+      <c r="H23" s="19">
+        <v>0</v>
+      </c>
+      <c r="I23" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
+        <v>0</v>
+      </c>
+      <c r="B24" s="18">
+        <v>0</v>
+      </c>
+      <c r="C24" s="18">
+        <v>0</v>
+      </c>
+      <c r="D24" s="18">
+        <v>0</v>
+      </c>
+      <c r="E24" s="18">
+        <v>0</v>
+      </c>
+      <c r="F24" s="18">
+        <v>2</v>
+      </c>
+      <c r="G24" s="19">
+        <v>0</v>
+      </c>
+      <c r="H24" s="19">
+        <v>0</v>
+      </c>
+      <c r="I24" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
+        <v>0</v>
+      </c>
+      <c r="B25" s="18">
+        <v>0</v>
+      </c>
+      <c r="C25" s="18">
+        <v>0</v>
+      </c>
+      <c r="D25" s="18">
+        <v>0</v>
+      </c>
+      <c r="E25" s="18">
+        <v>0</v>
+      </c>
+      <c r="F25" s="18">
+        <v>0</v>
+      </c>
+      <c r="G25" s="18">
+        <v>1</v>
+      </c>
+      <c r="H25" s="19">
+        <v>0</v>
+      </c>
+      <c r="I25" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="18">
+        <v>0</v>
+      </c>
+      <c r="B26" s="18">
+        <v>0</v>
+      </c>
+      <c r="C26" s="18">
+        <v>0</v>
+      </c>
+      <c r="D26" s="18">
+        <v>1</v>
+      </c>
+      <c r="E26" s="18">
+        <v>0</v>
+      </c>
+      <c r="F26" s="18">
+        <v>0</v>
+      </c>
+      <c r="G26" s="18">
+        <v>1</v>
+      </c>
+      <c r="H26" s="19">
+        <v>0</v>
+      </c>
+      <c r="I26" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
+        <v>0</v>
+      </c>
+      <c r="B27" s="18">
+        <v>0</v>
+      </c>
+      <c r="C27" s="18">
+        <v>0</v>
+      </c>
+      <c r="D27" s="18">
+        <v>1</v>
+      </c>
+      <c r="E27" s="18">
+        <v>0</v>
+      </c>
+      <c r="F27" s="18">
+        <v>0</v>
+      </c>
+      <c r="G27" s="18">
+        <v>1</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="18">
+        <v>0</v>
+      </c>
+      <c r="B28" s="18">
+        <v>0</v>
+      </c>
+      <c r="C28" s="18">
+        <v>1</v>
+      </c>
+      <c r="D28" s="18">
+        <v>0</v>
+      </c>
+      <c r="E28" s="18">
+        <v>0</v>
+      </c>
+      <c r="F28" s="18">
+        <v>0</v>
+      </c>
+      <c r="G28" s="18">
+        <v>1</v>
+      </c>
+      <c r="H28" s="19">
+        <v>0</v>
+      </c>
+      <c r="I28" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="18">
+        <v>0</v>
+      </c>
+      <c r="B29" s="18">
+        <v>0</v>
+      </c>
+      <c r="C29" s="18">
+        <v>0</v>
+      </c>
+      <c r="D29" s="18">
+        <v>0</v>
+      </c>
+      <c r="E29" s="18">
+        <v>1</v>
+      </c>
+      <c r="F29" s="18">
+        <v>0</v>
+      </c>
+      <c r="G29" s="18">
+        <v>1</v>
+      </c>
+      <c r="H29" s="19">
+        <v>0</v>
+      </c>
+      <c r="I29" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
+        <v>0</v>
+      </c>
+      <c r="B31" s="19">
+        <v>0</v>
+      </c>
+      <c r="C31" s="19">
+        <v>1</v>
+      </c>
+      <c r="D31" s="19">
+        <v>0</v>
+      </c>
+      <c r="E31" s="19">
+        <v>1</v>
+      </c>
+      <c r="F31" s="19">
+        <v>0</v>
+      </c>
+      <c r="G31" s="19">
+        <v>0</v>
+      </c>
+      <c r="H31" s="19">
+        <v>0</v>
+      </c>
+      <c r="I31" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
+        <v>0</v>
+      </c>
+      <c r="B32" s="19">
+        <v>0</v>
+      </c>
+      <c r="C32" s="19">
+        <v>0</v>
+      </c>
+      <c r="D32" s="19">
+        <v>1</v>
+      </c>
+      <c r="E32" s="19">
+        <v>1</v>
+      </c>
+      <c r="F32" s="19">
+        <v>0</v>
+      </c>
+      <c r="G32" s="19">
+        <v>0</v>
+      </c>
+      <c r="H32" s="19">
+        <v>0</v>
+      </c>
+      <c r="I32" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
+        <v>0</v>
+      </c>
+      <c r="B33" s="19">
+        <v>0</v>
+      </c>
+      <c r="C33" s="19">
+        <v>0</v>
+      </c>
+      <c r="D33" s="19">
+        <v>1</v>
+      </c>
+      <c r="E33" s="19">
+        <v>0</v>
+      </c>
+      <c r="F33" s="19">
+        <v>0</v>
+      </c>
+      <c r="G33" s="19">
+        <v>0</v>
+      </c>
+      <c r="H33" s="19">
+        <v>1</v>
+      </c>
+      <c r="I33" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="19">
+        <v>0</v>
+      </c>
+      <c r="B34" s="19">
+        <v>0</v>
+      </c>
+      <c r="C34" s="19">
+        <v>1</v>
+      </c>
+      <c r="D34" s="19">
+        <v>0</v>
+      </c>
+      <c r="E34" s="19">
+        <v>0</v>
+      </c>
+      <c r="F34" s="19">
+        <v>0</v>
+      </c>
+      <c r="G34" s="19">
+        <v>0</v>
+      </c>
+      <c r="H34" s="19">
+        <v>1</v>
+      </c>
+      <c r="I34" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="19">
+        <v>0</v>
+      </c>
+      <c r="B35" s="19">
+        <v>1</v>
+      </c>
+      <c r="C35" s="19">
+        <v>0</v>
+      </c>
+      <c r="D35" s="19">
+        <v>0</v>
+      </c>
+      <c r="E35" s="19">
+        <v>0</v>
+      </c>
+      <c r="F35" s="19">
+        <v>0</v>
+      </c>
+      <c r="G35" s="19">
+        <v>0</v>
+      </c>
+      <c r="H35" s="19">
+        <v>0</v>
+      </c>
+      <c r="I35" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="19">
+        <v>1</v>
+      </c>
+      <c r="B36" s="19">
+        <v>0</v>
+      </c>
+      <c r="C36" s="19">
+        <v>0</v>
+      </c>
+      <c r="D36" s="19">
+        <v>0</v>
+      </c>
+      <c r="E36" s="19">
+        <v>0</v>
+      </c>
+      <c r="F36" s="19">
+        <v>0</v>
+      </c>
+      <c r="G36" s="19">
+        <v>0</v>
+      </c>
+      <c r="H36" s="19">
+        <v>0</v>
+      </c>
+      <c r="I36" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="19">
+        <v>2</v>
+      </c>
+      <c r="B37" s="19">
+        <v>0</v>
+      </c>
+      <c r="C37" s="19">
+        <v>0</v>
+      </c>
+      <c r="D37" s="19">
+        <v>0</v>
+      </c>
+      <c r="E37" s="19">
+        <v>0</v>
+      </c>
+      <c r="F37" s="19">
+        <v>0</v>
+      </c>
+      <c r="G37" s="19">
+        <v>0</v>
+      </c>
+      <c r="H37" s="19">
+        <v>0</v>
+      </c>
+      <c r="I37" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="19">
+        <v>1</v>
+      </c>
+      <c r="B38" s="19">
+        <v>0</v>
+      </c>
+      <c r="C38" s="19">
+        <v>0</v>
+      </c>
+      <c r="D38" s="19">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19">
+        <v>0</v>
+      </c>
+      <c r="F38" s="19">
+        <v>0</v>
+      </c>
+      <c r="G38" s="19">
+        <v>0</v>
+      </c>
+      <c r="H38" s="19">
+        <v>1</v>
+      </c>
+      <c r="I38" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="19">
+        <v>0</v>
+      </c>
+      <c r="B39" s="19">
+        <v>0</v>
+      </c>
+      <c r="C39" s="19">
+        <v>0</v>
+      </c>
+      <c r="D39" s="19">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19">
+        <v>0</v>
+      </c>
+      <c r="F39" s="19">
+        <v>0</v>
+      </c>
+      <c r="G39" s="19">
+        <v>0</v>
+      </c>
+      <c r="H39" s="19">
+        <v>1</v>
+      </c>
+      <c r="I39" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="19">
+        <v>0</v>
+      </c>
+      <c r="B40" s="19">
+        <v>0</v>
+      </c>
+      <c r="C40" s="19">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19">
+        <v>0</v>
+      </c>
+      <c r="F40" s="19">
+        <v>1</v>
+      </c>
+      <c r="G40" s="19">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19">
+        <v>0</v>
+      </c>
+      <c r="I40" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="19">
+        <v>1</v>
+      </c>
+      <c r="B41" s="19">
+        <v>0</v>
+      </c>
+      <c r="C41" s="19">
+        <v>0</v>
+      </c>
+      <c r="D41" s="19">
+        <v>0</v>
+      </c>
+      <c r="E41" s="19">
+        <v>0</v>
+      </c>
+      <c r="F41" s="19">
+        <v>1</v>
+      </c>
+      <c r="G41" s="19">
+        <v>0</v>
+      </c>
+      <c r="H41" s="19">
+        <v>0</v>
+      </c>
+      <c r="I41" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="19">
+        <v>0</v>
+      </c>
+      <c r="B42" s="19">
+        <v>1</v>
+      </c>
+      <c r="C42" s="19">
+        <v>0</v>
+      </c>
+      <c r="D42" s="19">
+        <v>0</v>
+      </c>
+      <c r="E42" s="19">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19">
+        <v>1</v>
+      </c>
+      <c r="G42" s="19">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19">
+        <v>0</v>
+      </c>
+      <c r="I42" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="19">
+        <v>0</v>
+      </c>
+      <c r="B43" s="19">
+        <v>0</v>
+      </c>
+      <c r="C43" s="19">
+        <v>0</v>
+      </c>
+      <c r="D43" s="19">
+        <v>0</v>
+      </c>
+      <c r="E43" s="19">
+        <v>0</v>
+      </c>
+      <c r="F43" s="19">
+        <v>1</v>
+      </c>
+      <c r="G43" s="19">
+        <v>0</v>
+      </c>
+      <c r="H43" s="19">
+        <v>0</v>
+      </c>
+      <c r="I43" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="19">
+        <v>0</v>
+      </c>
+      <c r="B44" s="19">
+        <v>0</v>
+      </c>
+      <c r="C44" s="19">
+        <v>0</v>
+      </c>
+      <c r="D44" s="19">
+        <v>0</v>
+      </c>
+      <c r="E44" s="19">
+        <v>0</v>
+      </c>
+      <c r="F44" s="19">
+        <v>1</v>
+      </c>
+      <c r="G44" s="19">
+        <v>0</v>
+      </c>
+      <c r="H44" s="19">
+        <v>1</v>
+      </c>
+      <c r="I44" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="19">
+        <v>0</v>
+      </c>
+      <c r="B45" s="19">
+        <v>0</v>
+      </c>
+      <c r="C45" s="19">
+        <v>0</v>
+      </c>
+      <c r="D45" s="19">
+        <v>0</v>
+      </c>
+      <c r="E45" s="19">
+        <v>2</v>
+      </c>
+      <c r="F45" s="19">
+        <v>0</v>
+      </c>
+      <c r="G45" s="19">
+        <v>0</v>
+      </c>
+      <c r="H45" s="19">
+        <v>0</v>
+      </c>
+      <c r="I45" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="19">
+        <v>1</v>
+      </c>
+      <c r="B46" s="19">
+        <v>1</v>
+      </c>
+      <c r="C46" s="19">
+        <v>0</v>
+      </c>
+      <c r="D46" s="19">
+        <v>0</v>
+      </c>
+      <c r="E46" s="19">
+        <v>0</v>
+      </c>
+      <c r="F46" s="19">
+        <v>0</v>
+      </c>
+      <c r="G46" s="19">
+        <v>0</v>
+      </c>
+      <c r="H46" s="19">
+        <v>0</v>
+      </c>
+      <c r="I46" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="19">
+        <v>0</v>
+      </c>
+      <c r="B47" s="19">
+        <v>0</v>
+      </c>
+      <c r="C47" s="19">
+        <v>1</v>
+      </c>
+      <c r="D47" s="19">
+        <v>0</v>
+      </c>
+      <c r="E47" s="19">
+        <v>0</v>
+      </c>
+      <c r="F47" s="19">
+        <v>0</v>
+      </c>
+      <c r="G47" s="19">
+        <v>0</v>
+      </c>
+      <c r="H47" s="19">
+        <v>1</v>
+      </c>
+      <c r="I47" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="19">
+        <v>0</v>
+      </c>
+      <c r="B48" s="19">
+        <v>1</v>
+      </c>
+      <c r="C48" s="19">
+        <v>0</v>
+      </c>
+      <c r="D48" s="19">
+        <v>0</v>
+      </c>
+      <c r="E48" s="19">
+        <v>1</v>
+      </c>
+      <c r="F48" s="19">
+        <v>0</v>
+      </c>
+      <c r="G48" s="19">
+        <v>0</v>
+      </c>
+      <c r="H48" s="19">
+        <v>0</v>
+      </c>
+      <c r="I48" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="19">
+        <v>0</v>
+      </c>
+      <c r="B49" s="19">
+        <v>1</v>
+      </c>
+      <c r="C49" s="19">
+        <v>0</v>
+      </c>
+      <c r="D49" s="19">
+        <v>0</v>
+      </c>
+      <c r="E49" s="19">
+        <v>0</v>
+      </c>
+      <c r="F49" s="19">
+        <v>0</v>
+      </c>
+      <c r="G49" s="19">
+        <v>0</v>
+      </c>
+      <c r="H49" s="19">
+        <v>1</v>
+      </c>
+      <c r="I49" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="19">
+        <v>0</v>
+      </c>
+      <c r="B50" s="19">
+        <v>1</v>
+      </c>
+      <c r="C50" s="19">
+        <v>0</v>
+      </c>
+      <c r="D50" s="19">
+        <v>0</v>
+      </c>
+      <c r="E50" s="18">
+        <v>0</v>
+      </c>
+      <c r="F50" s="19">
+        <v>0</v>
+      </c>
+      <c r="G50" s="18">
+        <v>1</v>
+      </c>
+      <c r="H50" s="18">
+        <v>0</v>
+      </c>
+      <c r="I50" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="19">
+        <v>0</v>
+      </c>
+      <c r="B51" s="18">
+        <v>0</v>
+      </c>
+      <c r="C51" s="19">
+        <v>0</v>
+      </c>
+      <c r="D51" s="19">
+        <v>0</v>
+      </c>
+      <c r="E51" s="18">
+        <v>2</v>
+      </c>
+      <c r="F51" s="19">
+        <v>0</v>
+      </c>
+      <c r="G51" s="18">
+        <v>0</v>
+      </c>
+      <c r="H51" s="18">
+        <v>0</v>
+      </c>
+      <c r="I51" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="18">
+        <v>1</v>
+      </c>
+      <c r="B52" s="18">
+        <v>0</v>
+      </c>
+      <c r="C52" s="19">
+        <v>0</v>
+      </c>
+      <c r="D52" s="19">
+        <v>0</v>
+      </c>
+      <c r="E52" s="18">
+        <v>0</v>
+      </c>
+      <c r="F52" s="18">
+        <v>1</v>
+      </c>
+      <c r="G52" s="18">
+        <v>0</v>
+      </c>
+      <c r="H52" s="18">
+        <v>0</v>
+      </c>
+      <c r="I52" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="18">
+        <v>0</v>
+      </c>
+      <c r="B53" s="18">
+        <v>0</v>
+      </c>
+      <c r="C53" s="19">
+        <v>0</v>
+      </c>
+      <c r="D53" s="19">
+        <v>0</v>
+      </c>
+      <c r="E53" s="18">
+        <v>1</v>
+      </c>
+      <c r="F53" s="18">
+        <v>0</v>
+      </c>
+      <c r="G53" s="18">
+        <v>0</v>
+      </c>
+      <c r="H53" s="18">
+        <v>1</v>
+      </c>
+      <c r="I53" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="18">
+        <v>0</v>
+      </c>
+      <c r="B54" s="18">
+        <v>0</v>
+      </c>
+      <c r="C54" s="19">
+        <v>0</v>
+      </c>
+      <c r="D54" s="19">
+        <v>0</v>
+      </c>
+      <c r="E54" s="18">
+        <v>1</v>
+      </c>
+      <c r="F54" s="18">
+        <v>1</v>
+      </c>
+      <c r="G54" s="18">
+        <v>0</v>
+      </c>
+      <c r="H54" s="18">
+        <v>0</v>
+      </c>
+      <c r="I54" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="18">
+        <v>0</v>
+      </c>
+      <c r="B55" s="18">
+        <v>0</v>
+      </c>
+      <c r="C55" s="19">
+        <v>0</v>
+      </c>
+      <c r="D55" s="19">
+        <v>0</v>
+      </c>
+      <c r="E55" s="18">
+        <v>0</v>
+      </c>
+      <c r="F55" s="18">
+        <v>1</v>
+      </c>
+      <c r="G55" s="18">
+        <v>0</v>
+      </c>
+      <c r="H55" s="18">
+        <v>1</v>
+      </c>
+      <c r="I55" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" s="19">
+        <v>0</v>
+      </c>
+      <c r="B57" s="19">
+        <v>0</v>
+      </c>
+      <c r="C57" s="19">
+        <v>0</v>
+      </c>
+      <c r="D57" s="19">
+        <v>0</v>
+      </c>
+      <c r="E57" s="19">
+        <v>0</v>
+      </c>
+      <c r="F57" s="19">
+        <v>0</v>
+      </c>
+      <c r="G57" s="19">
+        <v>0</v>
+      </c>
+      <c r="H57" s="19">
+        <v>0</v>
+      </c>
+      <c r="I57" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="19">
+        <v>0</v>
+      </c>
+      <c r="B58" s="19">
+        <v>0</v>
+      </c>
+      <c r="C58" s="19">
+        <v>0</v>
+      </c>
+      <c r="D58" s="19">
+        <v>0</v>
+      </c>
+      <c r="E58" s="19">
+        <v>0</v>
+      </c>
+      <c r="F58" s="19">
+        <v>0</v>
+      </c>
+      <c r="G58" s="19">
+        <v>0</v>
+      </c>
+      <c r="H58" s="19">
+        <v>0</v>
+      </c>
+      <c r="I58" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="19">
+        <v>0</v>
+      </c>
+      <c r="B59" s="19">
+        <v>0</v>
+      </c>
+      <c r="C59" s="19">
+        <v>0</v>
+      </c>
+      <c r="D59" s="19">
+        <v>0</v>
+      </c>
+      <c r="E59" s="19">
+        <v>0</v>
+      </c>
+      <c r="F59" s="19">
+        <v>0</v>
+      </c>
+      <c r="G59" s="19">
+        <v>0</v>
+      </c>
+      <c r="H59" s="19">
+        <v>0</v>
+      </c>
+      <c r="I59" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="19">
+        <v>0</v>
+      </c>
+      <c r="B60" s="19">
+        <v>0</v>
+      </c>
+      <c r="C60" s="19">
+        <v>0</v>
+      </c>
+      <c r="D60" s="19">
+        <v>0</v>
+      </c>
+      <c r="E60" s="19">
+        <v>0</v>
+      </c>
+      <c r="F60" s="19">
+        <v>0</v>
+      </c>
+      <c r="G60" s="19">
+        <v>0</v>
+      </c>
+      <c r="H60" s="19">
+        <v>0</v>
+      </c>
+      <c r="I60" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" s="19">
+        <v>2.9</v>
+      </c>
+      <c r="B61" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="C61" s="19">
+        <v>1</v>
+      </c>
+      <c r="D61" s="19">
+        <v>1</v>
+      </c>
+      <c r="E61" s="19">
+        <v>1</v>
+      </c>
+      <c r="F61" s="19">
+        <v>1</v>
+      </c>
+      <c r="G61" s="19">
+        <v>1</v>
+      </c>
+      <c r="H61" s="19">
+        <v>18.5</v>
+      </c>
+      <c r="I61" s="19">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" s="19">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="B62" s="19">
+        <v>1.6</v>
+      </c>
+      <c r="C62" s="19">
+        <v>1</v>
+      </c>
+      <c r="D62" s="19">
+        <v>1</v>
+      </c>
+      <c r="E62" s="19">
+        <v>1</v>
+      </c>
+      <c r="F62" s="19">
+        <v>1</v>
+      </c>
+      <c r="G62" s="19">
+        <v>1</v>
+      </c>
+      <c r="H62" s="19">
+        <v>23.56</v>
+      </c>
+      <c r="I62" s="19">
+        <v>1.6</v>
+      </c>
+      <c r="J62" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K62" s="19">
+        <v>1.6</v>
+      </c>
+      <c r="L62" s="19">
+        <v>1</v>
+      </c>
+      <c r="M62" s="19">
+        <v>1</v>
+      </c>
+      <c r="N62" s="19">
+        <v>1</v>
+      </c>
+      <c r="O62" s="19">
+        <v>1</v>
+      </c>
+      <c r="P62" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="R62" s="19">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" s="19">
+        <v>0</v>
+      </c>
+      <c r="B63" s="19">
+        <v>0</v>
+      </c>
+      <c r="C63" s="19">
+        <v>0</v>
+      </c>
+      <c r="D63" s="19">
+        <v>0</v>
+      </c>
+      <c r="E63" s="19">
+        <v>0</v>
+      </c>
+      <c r="F63" s="19">
+        <v>0</v>
+      </c>
+      <c r="G63" s="19">
+        <v>0</v>
+      </c>
+      <c r="H63" s="19">
+        <v>0</v>
+      </c>
+      <c r="I63" s="19">
+        <v>0</v>
+      </c>
+      <c r="J63" s="19">
+        <v>0</v>
+      </c>
+      <c r="K63" s="19">
+        <v>0</v>
+      </c>
+      <c r="L63" s="19">
+        <v>0</v>
+      </c>
+      <c r="M63" s="19">
+        <v>0</v>
+      </c>
+      <c r="N63" s="19">
+        <v>0</v>
+      </c>
+      <c r="O63" s="19">
+        <v>0</v>
+      </c>
+      <c r="P63" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="19">
+        <v>0</v>
+      </c>
+      <c r="R63" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="19">
+        <v>0</v>
+      </c>
+      <c r="B64" s="19">
+        <v>0</v>
+      </c>
+      <c r="C64" s="19">
+        <v>0</v>
+      </c>
+      <c r="D64" s="19">
+        <v>0</v>
+      </c>
+      <c r="E64" s="19">
+        <v>0</v>
+      </c>
+      <c r="F64" s="19">
+        <v>0</v>
+      </c>
+      <c r="G64" s="19">
+        <v>0</v>
+      </c>
+      <c r="H64" s="19">
+        <v>0</v>
+      </c>
+      <c r="I64" s="19">
+        <v>0</v>
+      </c>
+      <c r="J64" s="19">
+        <v>0</v>
+      </c>
+      <c r="K64" s="19">
+        <v>0</v>
+      </c>
+      <c r="L64" s="19">
+        <v>0</v>
+      </c>
+      <c r="M64" s="19">
+        <v>0</v>
+      </c>
+      <c r="N64" s="19">
+        <v>0</v>
+      </c>
+      <c r="O64" s="19">
+        <v>0</v>
+      </c>
+      <c r="P64" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="19">
+        <v>0</v>
+      </c>
+      <c r="R64" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A65" s="19">
+        <v>1.9</v>
+      </c>
+      <c r="B65" s="19">
+        <v>2.6</v>
+      </c>
+      <c r="C65" s="19">
+        <v>1</v>
+      </c>
+      <c r="D65" s="19">
+        <v>1</v>
+      </c>
+      <c r="E65" s="19">
+        <v>1</v>
+      </c>
+      <c r="F65" s="19">
+        <v>1</v>
+      </c>
+      <c r="G65" s="19">
+        <v>1</v>
+      </c>
+      <c r="H65" s="19">
+        <v>9.5</v>
+      </c>
+      <c r="I65" s="19">
+        <v>2.6</v>
+      </c>
+      <c r="J65" s="19">
+        <v>1.9</v>
+      </c>
+      <c r="K65" s="19">
+        <v>2.6</v>
+      </c>
+      <c r="L65" s="19">
+        <v>1</v>
+      </c>
+      <c r="M65" s="19">
+        <v>1</v>
+      </c>
+      <c r="N65" s="19">
+        <v>1</v>
+      </c>
+      <c r="O65" s="19">
+        <v>1</v>
+      </c>
+      <c r="P65" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="19">
+        <v>9.5</v>
+      </c>
+      <c r="R65" s="19">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66" s="19">
+        <v>2.64</v>
+      </c>
+      <c r="B66" s="19">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="C66" s="19">
+        <v>1</v>
+      </c>
+      <c r="D66" s="19">
+        <v>1</v>
+      </c>
+      <c r="E66" s="19">
+        <v>1</v>
+      </c>
+      <c r="F66" s="19">
+        <v>1</v>
+      </c>
+      <c r="G66" s="19">
+        <v>1</v>
+      </c>
+      <c r="H66" s="19">
+        <v>17.66</v>
+      </c>
+      <c r="I66" s="19">
+        <v>0.93</v>
+      </c>
+      <c r="J66" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="K66" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="L66" s="19">
+        <v>1</v>
+      </c>
+      <c r="M66" s="19">
+        <v>1</v>
+      </c>
+      <c r="N66" s="19">
+        <v>1</v>
+      </c>
+      <c r="O66" s="19">
+        <v>1</v>
+      </c>
+      <c r="P66" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="R66" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A67" s="19">
+        <v>0</v>
+      </c>
+      <c r="B67" s="19">
+        <v>0</v>
+      </c>
+      <c r="C67" s="19">
+        <v>0</v>
+      </c>
+      <c r="D67" s="19">
+        <v>0</v>
+      </c>
+      <c r="E67" s="19">
+        <v>0</v>
+      </c>
+      <c r="F67" s="19">
+        <v>0</v>
+      </c>
+      <c r="G67" s="19">
+        <v>0</v>
+      </c>
+      <c r="H67" s="19">
+        <v>0</v>
+      </c>
+      <c r="I67" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A68" s="19">
+        <v>0</v>
+      </c>
+      <c r="B68" s="19">
+        <v>0</v>
+      </c>
+      <c r="C68" s="19">
+        <v>0</v>
+      </c>
+      <c r="D68" s="19">
+        <v>0</v>
+      </c>
+      <c r="E68" s="19">
+        <v>0</v>
+      </c>
+      <c r="F68" s="19">
+        <v>0</v>
+      </c>
+      <c r="G68" s="19">
+        <v>0</v>
+      </c>
+      <c r="H68" s="19">
+        <v>0</v>
+      </c>
+      <c r="I68" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" s="19">
+        <v>0</v>
+      </c>
+      <c r="B69" s="19">
+        <v>0</v>
+      </c>
+      <c r="C69" s="19">
+        <v>0</v>
+      </c>
+      <c r="D69" s="19">
+        <v>0</v>
+      </c>
+      <c r="E69" s="19">
+        <v>0</v>
+      </c>
+      <c r="F69" s="19">
+        <v>0</v>
+      </c>
+      <c r="G69" s="19">
+        <v>0</v>
+      </c>
+      <c r="H69" s="19">
+        <v>0</v>
+      </c>
+      <c r="I69" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A70" s="19">
+        <v>0</v>
+      </c>
+      <c r="B70" s="19">
+        <v>0</v>
+      </c>
+      <c r="C70" s="19">
+        <v>0</v>
+      </c>
+      <c r="D70" s="19">
+        <v>0</v>
+      </c>
+      <c r="E70" s="19">
+        <v>0</v>
+      </c>
+      <c r="F70" s="19">
+        <v>0</v>
+      </c>
+      <c r="G70" s="19">
+        <v>0</v>
+      </c>
+      <c r="H70" s="19">
+        <v>0</v>
+      </c>
+      <c r="I70" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71" s="19">
+        <v>0</v>
+      </c>
+      <c r="B71" s="19">
+        <v>0</v>
+      </c>
+      <c r="C71" s="19">
+        <v>0</v>
+      </c>
+      <c r="D71" s="19">
+        <v>0</v>
+      </c>
+      <c r="E71" s="19">
+        <v>0</v>
+      </c>
+      <c r="F71" s="19">
+        <v>0</v>
+      </c>
+      <c r="G71" s="19">
+        <v>0</v>
+      </c>
+      <c r="H71" s="19">
+        <v>0</v>
+      </c>
+      <c r="I71" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A72" s="19">
+        <v>0</v>
+      </c>
+      <c r="B72" s="19">
+        <v>0</v>
+      </c>
+      <c r="C72" s="19">
+        <v>0</v>
+      </c>
+      <c r="D72" s="19">
+        <v>0</v>
+      </c>
+      <c r="E72" s="19">
+        <v>0</v>
+      </c>
+      <c r="F72" s="19">
+        <v>0</v>
+      </c>
+      <c r="G72" s="19">
+        <v>0</v>
+      </c>
+      <c r="H72" s="19">
+        <v>0</v>
+      </c>
+      <c r="I72" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" s="19">
+        <v>0</v>
+      </c>
+      <c r="B73" s="19">
+        <v>0</v>
+      </c>
+      <c r="C73" s="19">
+        <v>0</v>
+      </c>
+      <c r="D73" s="19">
+        <v>0</v>
+      </c>
+      <c r="E73" s="19">
+        <v>0</v>
+      </c>
+      <c r="F73" s="19">
+        <v>0</v>
+      </c>
+      <c r="G73" s="19">
+        <v>0</v>
+      </c>
+      <c r="H73" s="19">
+        <v>0</v>
+      </c>
+      <c r="I73" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74" s="19">
+        <v>0</v>
+      </c>
+      <c r="B74" s="19">
+        <v>0</v>
+      </c>
+      <c r="C74" s="19">
+        <v>0</v>
+      </c>
+      <c r="D74" s="19">
+        <v>0</v>
+      </c>
+      <c r="E74" s="19">
+        <v>0</v>
+      </c>
+      <c r="F74" s="19">
+        <v>0</v>
+      </c>
+      <c r="G74" s="19">
+        <v>0</v>
+      </c>
+      <c r="H74" s="19">
+        <v>0</v>
+      </c>
+      <c r="I74" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A75" s="19">
+        <v>0</v>
+      </c>
+      <c r="B75" s="19">
+        <v>0</v>
+      </c>
+      <c r="C75" s="19">
+        <v>0</v>
+      </c>
+      <c r="D75" s="19">
+        <v>0</v>
+      </c>
+      <c r="E75" s="19">
+        <v>0</v>
+      </c>
+      <c r="F75" s="19">
+        <v>0</v>
+      </c>
+      <c r="G75" s="19">
+        <v>0</v>
+      </c>
+      <c r="H75" s="19">
+        <v>0</v>
+      </c>
+      <c r="I75" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A76" s="19">
+        <v>0</v>
+      </c>
+      <c r="B76" s="19">
+        <v>0</v>
+      </c>
+      <c r="C76" s="19">
+        <v>0</v>
+      </c>
+      <c r="D76" s="19">
+        <v>0</v>
+      </c>
+      <c r="E76" s="19">
+        <v>0</v>
+      </c>
+      <c r="F76" s="19">
+        <v>0</v>
+      </c>
+      <c r="G76" s="19">
+        <v>0</v>
+      </c>
+      <c r="H76" s="19">
+        <v>0</v>
+      </c>
+      <c r="I76" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A77" s="19">
+        <v>1.9</v>
+      </c>
+      <c r="B77" s="19">
+        <v>2.6</v>
+      </c>
+      <c r="C77" s="19">
+        <v>1</v>
+      </c>
+      <c r="D77" s="19">
+        <v>1</v>
+      </c>
+      <c r="E77" s="19">
+        <v>1</v>
+      </c>
+      <c r="F77" s="19">
+        <v>1</v>
+      </c>
+      <c r="G77" s="19">
+        <v>1</v>
+      </c>
+      <c r="H77" s="19">
+        <v>9.5</v>
+      </c>
+      <c r="I77" s="19">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78" s="19">
+        <v>0</v>
+      </c>
+      <c r="B78" s="19">
+        <v>0</v>
+      </c>
+      <c r="C78" s="19">
+        <v>0</v>
+      </c>
+      <c r="D78" s="19">
+        <v>0</v>
+      </c>
+      <c r="E78" s="19">
+        <v>0</v>
+      </c>
+      <c r="F78" s="19">
+        <v>0</v>
+      </c>
+      <c r="G78" s="19">
+        <v>0</v>
+      </c>
+      <c r="H78" s="19">
+        <v>0</v>
+      </c>
+      <c r="I78" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A79" s="19">
+        <v>0</v>
+      </c>
+      <c r="B79" s="19">
+        <v>0</v>
+      </c>
+      <c r="C79" s="19">
+        <v>0</v>
+      </c>
+      <c r="D79" s="19">
+        <v>0</v>
+      </c>
+      <c r="E79" s="19">
+        <v>0</v>
+      </c>
+      <c r="F79" s="19">
+        <v>0</v>
+      </c>
+      <c r="G79" s="19">
+        <v>0</v>
+      </c>
+      <c r="H79" s="19">
+        <v>0</v>
+      </c>
+      <c r="I79" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A80" s="19">
+        <v>0</v>
+      </c>
+      <c r="B80" s="19">
+        <v>0</v>
+      </c>
+      <c r="C80" s="19">
+        <v>0</v>
+      </c>
+      <c r="D80" s="19">
+        <v>0</v>
+      </c>
+      <c r="E80" s="19">
+        <v>0</v>
+      </c>
+      <c r="F80" s="19">
+        <v>0</v>
+      </c>
+      <c r="G80" s="19">
+        <v>0</v>
+      </c>
+      <c r="H80" s="19">
+        <v>0</v>
+      </c>
+      <c r="I80" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="19">
+        <v>0</v>
+      </c>
+      <c r="B81" s="19">
+        <v>0</v>
+      </c>
+      <c r="C81" s="19">
+        <v>0</v>
+      </c>
+      <c r="D81" s="19">
+        <v>0</v>
+      </c>
+      <c r="E81" s="19">
+        <v>0</v>
+      </c>
+      <c r="F81" s="19">
+        <v>0</v>
+      </c>
+      <c r="G81" s="19">
+        <v>0</v>
+      </c>
+      <c r="H81" s="19">
+        <v>0</v>
+      </c>
+      <c r="I81" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" s="17"/>
+      <c r="C82" s="14"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="14">
+        <v>2.6389999999999997E-7</v>
+      </c>
+      <c r="B83" s="15">
+        <v>-0.92700000000000005</v>
+      </c>
+      <c r="C83" s="14">
+        <v>-8492</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="14">
+        <v>8.3979999999999998E-20</v>
+      </c>
+      <c r="B84" s="15">
+        <v>2.67</v>
+      </c>
+      <c r="C84" s="14">
+        <v>-3163</v>
+      </c>
+      <c r="D84" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="14">
+        <v>3.5850000000000001E-16</v>
+      </c>
+      <c r="B85" s="15">
+        <v>1.51</v>
+      </c>
+      <c r="C85" s="14">
+        <v>-1726</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B86" s="15">
+        <v>1.4</v>
+      </c>
+      <c r="C86" s="14">
+        <v>199.7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="14">
+        <v>2.7549999999999999E-31</v>
+      </c>
+      <c r="B87" s="15">
+        <v>-1</v>
+      </c>
+      <c r="C87" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="14">
+        <v>1.7630000000000002E-30</v>
+      </c>
+      <c r="B88" s="15">
+        <v>-1</v>
+      </c>
+      <c r="C88" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="14">
+        <v>2.5340000000000001E-31</v>
+      </c>
+      <c r="B89" s="15">
+        <v>-0.6</v>
+      </c>
+      <c r="C89" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="14">
+        <v>1.653E-28</v>
+      </c>
+      <c r="B90" s="15">
+        <v>-1.25</v>
+      </c>
+      <c r="C90" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="14">
+        <v>2.3139999999999999E-26</v>
+      </c>
+      <c r="B91" s="15">
+        <v>-2</v>
+      </c>
+      <c r="C91" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="14">
+        <v>1.9279999999999999E-30</v>
+      </c>
+      <c r="B92" s="15">
+        <v>-0.8</v>
+      </c>
+      <c r="C92" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="14">
+        <v>7.7129999999999996E-30</v>
+      </c>
+      <c r="B93" s="15">
+        <v>-0.86</v>
+      </c>
+      <c r="C93" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="14">
+        <v>8.2640000000000005E-28</v>
+      </c>
+      <c r="B94" s="15">
+        <v>-1.72</v>
+      </c>
+      <c r="C94" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="14">
+        <v>1.0329999999999999E-27</v>
+      </c>
+      <c r="B95" s="15">
+        <v>-1.72</v>
+      </c>
+      <c r="C95" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="14">
+        <v>2.5899999999999999E-29</v>
+      </c>
+      <c r="B96" s="15">
+        <v>-0.76</v>
+      </c>
+      <c r="C96" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="14">
+        <v>3.6519999999999999E-10</v>
+      </c>
+      <c r="B97" s="15">
+        <v>0</v>
+      </c>
+      <c r="C97" s="14">
+        <v>-709.6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="14">
+        <v>4.1489999999999997E-11</v>
+      </c>
+      <c r="B98" s="15">
+        <v>0</v>
+      </c>
+      <c r="C98" s="14">
+        <v>-348.8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="14">
+        <v>8.2989999999999993E-12</v>
+      </c>
+      <c r="B99" s="15">
+        <v>0</v>
+      </c>
+      <c r="C99" s="14">
+        <v>-709.6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="14">
+        <v>3.3199999999999999E-11</v>
+      </c>
+      <c r="B100" s="15">
+        <v>0</v>
+      </c>
+      <c r="C100" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="14">
+        <v>3.3199999999999999E-11</v>
+      </c>
+      <c r="B101" s="15">
+        <v>0</v>
+      </c>
+      <c r="C101" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="16">
+        <v>1.7589999999999999E-13</v>
+      </c>
+      <c r="B102" s="17">
+        <v>0</v>
+      </c>
+      <c r="C102" s="16">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="16">
+        <v>1.66E-7</v>
+      </c>
+      <c r="B103" s="17">
+        <v>0</v>
+      </c>
+      <c r="C103" s="16">
+        <v>-23380</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="16">
+        <v>2.8219999999999999E-12</v>
+      </c>
+      <c r="B104" s="17">
+        <v>0</v>
+      </c>
+      <c r="C104" s="16">
+        <v>-1900</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="16">
+        <v>1.66E-11</v>
+      </c>
+      <c r="B105" s="17">
+        <v>0</v>
+      </c>
+      <c r="C105" s="16">
+        <v>-1804</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="16">
+        <v>4.6470000000000002E-11</v>
+      </c>
+      <c r="B106" s="17">
+        <v>0</v>
+      </c>
+      <c r="C106" s="16">
+        <v>-3223</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="16">
+        <v>1.1619999999999999E-11</v>
+      </c>
+      <c r="B107" s="17">
+        <v>0</v>
+      </c>
+      <c r="C107" s="16">
+        <v>-721.7</v>
       </c>
     </row>
   </sheetData>
